--- a/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/дв 28,07,26 лгрсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/дв 28,07,26 лгрсч ост сыр.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC288D2-2C94-4886-88CA-A86CEDA0BCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCEACD1-60F9-4420-9AA7-97A45EBD283E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,22 @@
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AD$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AE$44</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="86">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -273,6 +281,15 @@
   <si>
     <t>400шт в уценку (24,07,26)</t>
   </si>
+  <si>
+    <t>ТК</t>
+  </si>
+  <si>
+    <t>убрать из заказа</t>
+  </si>
+  <si>
+    <t>Чепрасова</t>
+  </si>
 </sst>
 </file>
 
@@ -319,7 +336,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,6 +362,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -384,7 +407,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -400,6 +423,11 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -703,7 +731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW500"/>
+  <dimension ref="A1:AX500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -717,14 +745,15 @@
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.5703125" customWidth="1"/>
     <col min="15" max="17" width="7" customWidth="1"/>
-    <col min="18" max="19" width="5" customWidth="1"/>
-    <col min="20" max="28" width="6" customWidth="1"/>
-    <col min="29" max="29" width="42.85546875" customWidth="1"/>
-    <col min="30" max="30" width="7" customWidth="1"/>
-    <col min="31" max="49" width="3" customWidth="1"/>
+    <col min="18" max="18" width="15.7109375" style="19" customWidth="1"/>
+    <col min="19" max="20" width="5" customWidth="1"/>
+    <col min="21" max="29" width="6" customWidth="1"/>
+    <col min="30" max="30" width="42.85546875" customWidth="1"/>
+    <col min="31" max="31" width="7" customWidth="1"/>
+    <col min="32" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -774,8 +803,9 @@
       <c r="AU1" s="1"/>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
-    </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX1" s="1"/>
+    </row>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -825,8 +855,9 @@
       <c r="AU2" s="1"/>
       <c r="AV2" s="1"/>
       <c r="AW2" s="1"/>
-    </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX2" s="1"/>
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -878,14 +909,14 @@
       <c r="Q3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>19</v>
@@ -912,12 +943,14 @@
         <v>19</v>
       </c>
       <c r="AC3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AD3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="AD3" s="2" t="s">
+      <c r="AE3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
       <c r="AG3" s="1"/>
       <c r="AH3" s="1"/>
@@ -936,8 +969,9 @@
       <c r="AU3" s="1"/>
       <c r="AV3" s="1"/>
       <c r="AW3" s="1"/>
-    </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX3" s="1"/>
+    </row>
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -959,36 +993,38 @@
         <v>23</v>
       </c>
       <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
+      <c r="R4" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="S4" s="1"/>
-      <c r="T4" s="1" t="s">
+      <c r="T4" s="1"/>
+      <c r="U4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="Z4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AA4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AC4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
@@ -1009,8 +1045,9 @@
       <c r="AU4" s="1"/>
       <c r="AV4" s="1"/>
       <c r="AW4" s="1"/>
-    </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX4" s="1"/>
+    </row>
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1055,50 +1092,50 @@
         <f t="shared" si="0"/>
         <v>3116.8675999999996</v>
       </c>
-      <c r="R5" s="1"/>
+      <c r="R5" s="4"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="4">
-        <f t="shared" ref="T5:AB5" si="1">SUM(T6:T500)</f>
+      <c r="T5" s="1"/>
+      <c r="U5" s="4">
+        <f t="shared" ref="U5:AC5" si="1">SUM(U6:U500)</f>
         <v>324.46199999999999</v>
       </c>
-      <c r="U5" s="4">
+      <c r="V5" s="4">
         <f t="shared" si="1"/>
         <v>420.2068000000001</v>
       </c>
-      <c r="V5" s="4">
+      <c r="W5" s="4">
         <f t="shared" si="1"/>
         <v>402.34719999999999</v>
       </c>
-      <c r="W5" s="4">
+      <c r="X5" s="4">
         <f t="shared" si="1"/>
         <v>299.33160000000004</v>
       </c>
-      <c r="X5" s="4">
+      <c r="Y5" s="4">
         <f t="shared" si="1"/>
         <v>358.81580000000002</v>
       </c>
-      <c r="Y5" s="4">
+      <c r="Z5" s="4">
         <f t="shared" si="1"/>
         <v>346.77240000000006</v>
       </c>
-      <c r="Z5" s="4">
+      <c r="AA5" s="4">
         <f t="shared" si="1"/>
         <v>374.9812</v>
       </c>
-      <c r="AA5" s="4">
+      <c r="AB5" s="4">
         <f t="shared" si="1"/>
         <v>347.31840000000011</v>
       </c>
-      <c r="AB5" s="4">
+      <c r="AC5" s="4">
         <f t="shared" si="1"/>
         <v>357.3904</v>
       </c>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="4">
-        <f>SUM(AD6:AD500)</f>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="4">
+        <f>SUM(AE6:AE500)</f>
         <v>733.46760000000006</v>
       </c>
-      <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
       <c r="AG5" s="1"/>
       <c r="AH5" s="1"/>
@@ -1117,8 +1154,9 @@
       <c r="AU5" s="1"/>
       <c r="AV5" s="1"/>
       <c r="AW5" s="1"/>
-    </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX5" s="1"/>
+    </row>
+    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>33</v>
       </c>
@@ -1156,17 +1194,15 @@
         <v>0.4</v>
       </c>
       <c r="Q6" s="5"/>
-      <c r="R6" s="1">
+      <c r="R6" s="16"/>
+      <c r="S6" s="1">
         <f>(F6+O6+Q6)/P6</f>
         <v>112.5</v>
       </c>
-      <c r="S6" s="1">
+      <c r="T6" s="1">
         <f>(F6+O6)/P6</f>
         <v>112.5</v>
       </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
       <c r="U6" s="1">
         <v>0</v>
       </c>
@@ -1191,14 +1227,16 @@
       <c r="AB6" s="1">
         <v>0</v>
       </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AC6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AD6" s="1">
+      <c r="AE6" s="1">
         <f>G6*Q6</f>
         <v>0</v>
       </c>
-      <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
@@ -1217,8 +1255,9 @@
       <c r="AU6" s="1"/>
       <c r="AV6" s="1"/>
       <c r="AW6" s="1"/>
-    </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX6" s="1"/>
+    </row>
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -1256,16 +1295,14 @@
         <v>0.4</v>
       </c>
       <c r="Q7" s="5"/>
-      <c r="R7" s="1">
-        <f t="shared" ref="R7:R44" si="4">(F7+O7+Q7)/P7</f>
+      <c r="R7" s="16"/>
+      <c r="S7" s="1">
+        <f t="shared" ref="S7:S44" si="4">(F7+O7+Q7)/P7</f>
         <v>100</v>
       </c>
-      <c r="S7" s="1">
-        <f t="shared" ref="S7:S44" si="5">(F7+O7)/P7</f>
+      <c r="T7" s="1">
+        <f t="shared" ref="T7:T44" si="5">(F7+O7)/P7</f>
         <v>100</v>
-      </c>
-      <c r="T7" s="1">
-        <v>0</v>
       </c>
       <c r="U7" s="1">
         <v>0</v>
@@ -1291,14 +1328,16 @@
       <c r="AB7" s="1">
         <v>0</v>
       </c>
-      <c r="AC7" s="1" t="s">
+      <c r="AC7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AD7" s="1">
+      <c r="AE7" s="1">
         <f>G7*Q7</f>
         <v>0</v>
       </c>
-      <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
@@ -1317,8 +1356,9 @@
       <c r="AU7" s="1"/>
       <c r="AV7" s="1"/>
       <c r="AW7" s="1"/>
-    </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX7" s="1"/>
+    </row>
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
@@ -1356,17 +1396,15 @@
         <v>0.4</v>
       </c>
       <c r="Q8" s="5"/>
-      <c r="R8" s="1">
+      <c r="R8" s="16"/>
+      <c r="S8" s="1">
         <f t="shared" si="4"/>
         <v>100</v>
       </c>
-      <c r="S8" s="1">
+      <c r="T8" s="1">
         <f t="shared" si="5"/>
         <v>100</v>
       </c>
-      <c r="T8" s="1">
-        <v>0</v>
-      </c>
       <c r="U8" s="1">
         <v>0</v>
       </c>
@@ -1391,14 +1429,16 @@
       <c r="AB8" s="1">
         <v>0</v>
       </c>
-      <c r="AC8" s="1" t="s">
+      <c r="AC8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AD8" s="1">
+      <c r="AE8" s="1">
         <f>G8*Q8</f>
         <v>0</v>
       </c>
-      <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="1"/>
@@ -1417,8 +1457,9 @@
       <c r="AU8" s="1"/>
       <c r="AV8" s="1"/>
       <c r="AW8" s="1"/>
-    </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX8" s="1"/>
+    </row>
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
@@ -1460,49 +1501,49 @@
         <v>7.5140000000000002</v>
       </c>
       <c r="Q9" s="5"/>
-      <c r="R9" s="1">
+      <c r="R9" s="16"/>
+      <c r="S9" s="1">
         <f t="shared" si="4"/>
         <v>65.868645195634812</v>
       </c>
-      <c r="S9" s="1">
+      <c r="T9" s="1">
         <f t="shared" si="5"/>
         <v>65.868645195634812</v>
       </c>
-      <c r="T9" s="1">
+      <c r="U9" s="1">
         <v>11.027200000000001</v>
       </c>
-      <c r="U9" s="1">
+      <c r="V9" s="1">
         <v>9.781600000000001</v>
       </c>
-      <c r="V9" s="1">
+      <c r="W9" s="1">
         <v>9.0831999999999997</v>
       </c>
-      <c r="W9" s="1">
+      <c r="X9" s="1">
         <v>6.6611999999999991</v>
       </c>
-      <c r="X9" s="1">
+      <c r="Y9" s="1">
         <v>7.8073999999999986</v>
       </c>
-      <c r="Y9" s="1">
+      <c r="Z9" s="1">
         <v>5.952</v>
       </c>
-      <c r="Z9" s="1">
+      <c r="AA9" s="1">
         <v>15.026400000000001</v>
       </c>
-      <c r="AA9" s="1">
+      <c r="AB9" s="1">
         <v>12.090400000000001</v>
       </c>
-      <c r="AB9" s="1">
+      <c r="AC9" s="1">
         <v>19.646799999999999</v>
       </c>
-      <c r="AC9" s="13" t="s">
+      <c r="AD9" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AD9" s="1">
+      <c r="AE9" s="1">
         <f>G9*Q9</f>
         <v>0</v>
       </c>
-      <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1"/>
       <c r="AH9" s="1"/>
@@ -1521,8 +1562,9 @@
       <c r="AU9" s="1"/>
       <c r="AV9" s="1"/>
       <c r="AW9" s="1"/>
-    </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX9" s="1"/>
+    </row>
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>40</v>
       </c>
@@ -1560,17 +1602,15 @@
         <v>0</v>
       </c>
       <c r="Q10" s="11"/>
-      <c r="R10" s="9" t="e">
+      <c r="R10" s="17"/>
+      <c r="S10" s="9" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S10" s="9" t="e">
+      <c r="T10" s="9" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T10" s="9">
-        <v>0</v>
-      </c>
       <c r="U10" s="9">
         <v>0</v>
       </c>
@@ -1578,10 +1618,10 @@
         <v>0</v>
       </c>
       <c r="W10" s="9">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9">
         <v>0.2</v>
-      </c>
-      <c r="X10" s="9">
-        <v>0</v>
       </c>
       <c r="Y10" s="9">
         <v>0</v>
@@ -1595,9 +1635,11 @@
       <c r="AB10" s="9">
         <v>0</v>
       </c>
-      <c r="AC10" s="9"/>
+      <c r="AC10" s="9">
+        <v>0</v>
+      </c>
       <c r="AD10" s="9"/>
-      <c r="AE10" s="1"/>
+      <c r="AE10" s="9"/>
       <c r="AF10" s="1"/>
       <c r="AG10" s="1"/>
       <c r="AH10" s="1"/>
@@ -1616,8 +1658,9 @@
       <c r="AU10" s="1"/>
       <c r="AV10" s="1"/>
       <c r="AW10" s="1"/>
-    </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX10" s="1"/>
+    </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -1659,19 +1702,17 @@
       <c r="Q11" s="5">
         <v>40</v>
       </c>
-      <c r="R11" s="1">
+      <c r="R11" s="16"/>
+      <c r="S11" s="1">
         <f t="shared" si="4"/>
         <v>14.583333333333334</v>
       </c>
-      <c r="S11" s="1">
+      <c r="T11" s="1">
         <f t="shared" si="5"/>
         <v>-2.0833333333333335</v>
       </c>
-      <c r="T11" s="1">
+      <c r="U11" s="1">
         <v>4.5999999999999996</v>
-      </c>
-      <c r="U11" s="1">
-        <v>0</v>
       </c>
       <c r="V11" s="1">
         <v>0</v>
@@ -1694,14 +1735,16 @@
       <c r="AB11" s="1">
         <v>0</v>
       </c>
-      <c r="AC11" s="12" t="s">
+      <c r="AC11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="AD11" s="1">
-        <f>G11*Q11</f>
+      <c r="AE11" s="1">
+        <f t="shared" ref="AE11:AE19" si="6">G11*Q11</f>
         <v>7.1999999999999993</v>
       </c>
-      <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
       <c r="AG11" s="1"/>
       <c r="AH11" s="1"/>
@@ -1720,8 +1763,9 @@
       <c r="AU11" s="1"/>
       <c r="AV11" s="1"/>
       <c r="AW11" s="1"/>
-    </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX11" s="1"/>
+    </row>
+    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>45</v>
       </c>
@@ -1763,19 +1807,17 @@
       <c r="Q12" s="5">
         <v>20</v>
       </c>
-      <c r="R12" s="1">
+      <c r="R12" s="16"/>
+      <c r="S12" s="1">
         <f t="shared" si="4"/>
         <v>18.75</v>
       </c>
-      <c r="S12" s="1">
+      <c r="T12" s="1">
         <f t="shared" si="5"/>
         <v>-6.25</v>
       </c>
-      <c r="T12" s="1">
+      <c r="U12" s="1">
         <v>5.6</v>
-      </c>
-      <c r="U12" s="1">
-        <v>0</v>
       </c>
       <c r="V12" s="1">
         <v>0</v>
@@ -1798,14 +1840,16 @@
       <c r="AB12" s="1">
         <v>0</v>
       </c>
-      <c r="AC12" s="12" t="s">
+      <c r="AC12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="AD12" s="1">
-        <f>G12*Q12</f>
+      <c r="AE12" s="1">
+        <f t="shared" si="6"/>
         <v>3.5999999999999996</v>
       </c>
-      <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1"/>
       <c r="AH12" s="1"/>
@@ -1824,8 +1868,9 @@
       <c r="AU12" s="1"/>
       <c r="AV12" s="1"/>
       <c r="AW12" s="1"/>
-    </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX12" s="1"/>
+    </row>
+    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>47</v>
       </c>
@@ -1865,49 +1910,49 @@
         <v>3.7276000000000002</v>
       </c>
       <c r="Q13" s="5"/>
-      <c r="R13" s="1">
+      <c r="R13" s="16"/>
+      <c r="S13" s="1">
         <f t="shared" si="4"/>
         <v>25.034070179203773</v>
       </c>
-      <c r="S13" s="1">
+      <c r="T13" s="1">
         <f t="shared" si="5"/>
         <v>25.034070179203773</v>
       </c>
-      <c r="T13" s="1">
+      <c r="U13" s="1">
         <v>2.6724000000000001</v>
       </c>
-      <c r="U13" s="1">
+      <c r="V13" s="1">
         <v>0.63600000000000001</v>
       </c>
-      <c r="V13" s="1">
+      <c r="W13" s="1">
         <v>2.7296</v>
       </c>
-      <c r="W13" s="1">
+      <c r="X13" s="1">
         <v>0</v>
       </c>
-      <c r="X13" s="1">
+      <c r="Y13" s="1">
         <v>3.2768000000000002</v>
       </c>
-      <c r="Y13" s="1">
+      <c r="Z13" s="1">
         <v>4.0444000000000004</v>
       </c>
-      <c r="Z13" s="1">
+      <c r="AA13" s="1">
         <v>1.9536</v>
-      </c>
-      <c r="AA13" s="1">
-        <v>0</v>
       </c>
       <c r="AB13" s="1">
         <v>0</v>
       </c>
-      <c r="AC13" s="13" t="s">
+      <c r="AC13" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AD13" s="1">
-        <f>G13*Q13</f>
+      <c r="AE13" s="1">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
@@ -1926,8 +1971,9 @@
       <c r="AU13" s="1"/>
       <c r="AV13" s="1"/>
       <c r="AW13" s="1"/>
-    </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX13" s="1"/>
+    </row>
+    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -1967,50 +2013,50 @@
         <v>1.8</v>
       </c>
       <c r="Q14" s="5">
-        <f t="shared" ref="Q11:Q19" si="6">20*P14-O14-F14</f>
+        <f t="shared" ref="Q14:Q17" si="7">20*P14-O14-F14</f>
         <v>24</v>
       </c>
-      <c r="R14" s="1">
+      <c r="R14" s="16"/>
+      <c r="S14" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S14" s="1">
+      <c r="T14" s="1">
         <f t="shared" si="5"/>
         <v>6.6666666666666661</v>
       </c>
-      <c r="T14" s="1">
-        <v>0.8</v>
-      </c>
       <c r="U14" s="1">
         <v>0.8</v>
       </c>
       <c r="V14" s="1">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="W14" s="1">
         <v>1</v>
       </c>
       <c r="X14" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="1">
         <v>2.4</v>
       </c>
-      <c r="Y14" s="1">
+      <c r="Z14" s="1">
         <v>0.4</v>
       </c>
-      <c r="Z14" s="1">
+      <c r="AA14" s="1">
         <v>0.6</v>
       </c>
-      <c r="AA14" s="1">
+      <c r="AB14" s="1">
         <v>1.2</v>
       </c>
-      <c r="AB14" s="1">
+      <c r="AC14" s="1">
         <v>1.4</v>
       </c>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1">
-        <f>G14*Q14</f>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1">
+        <f t="shared" si="6"/>
         <v>19.788</v>
       </c>
-      <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
       <c r="AG14" s="1"/>
       <c r="AH14" s="1"/>
@@ -2029,8 +2075,9 @@
       <c r="AU14" s="1"/>
       <c r="AV14" s="1"/>
       <c r="AW14" s="1"/>
-    </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX14" s="1"/>
+    </row>
+    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>49</v>
       </c>
@@ -2072,50 +2119,50 @@
         <v>24.4</v>
       </c>
       <c r="Q15" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>186</v>
       </c>
-      <c r="R15" s="1">
+      <c r="R15" s="16"/>
+      <c r="S15" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S15" s="1">
+      <c r="T15" s="1">
         <f t="shared" si="5"/>
         <v>12.377049180327869</v>
       </c>
-      <c r="T15" s="1">
+      <c r="U15" s="1">
         <v>11.6</v>
       </c>
-      <c r="U15" s="1">
+      <c r="V15" s="1">
         <v>25.2</v>
       </c>
-      <c r="V15" s="1">
+      <c r="W15" s="1">
         <v>28.2</v>
       </c>
-      <c r="W15" s="1">
+      <c r="X15" s="1">
         <v>10.4</v>
       </c>
-      <c r="X15" s="1">
+      <c r="Y15" s="1">
         <v>15.4</v>
       </c>
-      <c r="Y15" s="1">
+      <c r="Z15" s="1">
         <v>20.2</v>
       </c>
-      <c r="Z15" s="1">
+      <c r="AA15" s="1">
         <v>21.8</v>
       </c>
-      <c r="AA15" s="1">
+      <c r="AB15" s="1">
         <v>30.8</v>
       </c>
-      <c r="AB15" s="1">
+      <c r="AC15" s="1">
         <v>3.4</v>
       </c>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1">
-        <f>G15*Q15</f>
+      <c r="AD15" s="1"/>
+      <c r="AE15" s="1">
+        <f t="shared" si="6"/>
         <v>69.191999999999993</v>
       </c>
-      <c r="AE15" s="1"/>
       <c r="AF15" s="1"/>
       <c r="AG15" s="1"/>
       <c r="AH15" s="1"/>
@@ -2134,8 +2181,9 @@
       <c r="AU15" s="1"/>
       <c r="AV15" s="1"/>
       <c r="AW15" s="1"/>
-    </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX15" s="1"/>
+    </row>
+    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>50</v>
       </c>
@@ -2177,49 +2225,49 @@
         <v>5.8</v>
       </c>
       <c r="Q16" s="5"/>
-      <c r="R16" s="1">
+      <c r="R16" s="16"/>
+      <c r="S16" s="1">
         <f t="shared" si="4"/>
         <v>70.172413793103445</v>
       </c>
-      <c r="S16" s="1">
+      <c r="T16" s="1">
         <f t="shared" si="5"/>
         <v>70.172413793103445</v>
       </c>
-      <c r="T16" s="1">
+      <c r="U16" s="1">
         <v>5.2</v>
       </c>
-      <c r="U16" s="1">
+      <c r="V16" s="1">
         <v>23</v>
       </c>
-      <c r="V16" s="1">
+      <c r="W16" s="1">
         <v>16.8</v>
       </c>
-      <c r="W16" s="1">
+      <c r="X16" s="1">
         <v>10.8</v>
       </c>
-      <c r="X16" s="1">
+      <c r="Y16" s="1">
         <v>8</v>
       </c>
-      <c r="Y16" s="1">
+      <c r="Z16" s="1">
         <v>19.399999999999999</v>
       </c>
-      <c r="Z16" s="1">
+      <c r="AA16" s="1">
         <v>20.2</v>
       </c>
-      <c r="AA16" s="1">
+      <c r="AB16" s="1">
         <v>30.2</v>
       </c>
-      <c r="AB16" s="1">
+      <c r="AC16" s="1">
         <v>17.399999999999999</v>
       </c>
-      <c r="AC16" s="14" t="s">
+      <c r="AD16" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AD16" s="1">
-        <f>G16*Q16</f>
+      <c r="AE16" s="1">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
       <c r="AH16" s="1"/>
@@ -2238,8 +2286,9 @@
       <c r="AU16" s="1"/>
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
-    </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX16" s="1"/>
+    </row>
+    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>51</v>
       </c>
@@ -2283,50 +2332,50 @@
         <v>47.4</v>
       </c>
       <c r="Q17" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>326</v>
       </c>
-      <c r="R17" s="1">
+      <c r="R17" s="16"/>
+      <c r="S17" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S17" s="1">
+      <c r="T17" s="1">
         <f t="shared" si="5"/>
         <v>13.122362869198312</v>
       </c>
-      <c r="T17" s="1">
+      <c r="U17" s="1">
         <v>41.4</v>
       </c>
-      <c r="U17" s="1">
+      <c r="V17" s="1">
         <v>44.2</v>
       </c>
-      <c r="V17" s="1">
+      <c r="W17" s="1">
         <v>38.6</v>
       </c>
-      <c r="W17" s="1">
+      <c r="X17" s="1">
         <v>32.4</v>
       </c>
-      <c r="X17" s="1">
+      <c r="Y17" s="1">
         <v>35</v>
       </c>
-      <c r="Y17" s="1">
+      <c r="Z17" s="1">
         <v>33.6</v>
       </c>
-      <c r="Z17" s="1">
+      <c r="AA17" s="1">
         <v>70.400000000000006</v>
       </c>
-      <c r="AA17" s="1">
+      <c r="AB17" s="1">
         <v>10.4</v>
       </c>
-      <c r="AB17" s="1">
+      <c r="AC17" s="1">
         <v>33.6</v>
       </c>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1">
-        <f>G17*Q17</f>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1">
+        <f t="shared" si="6"/>
         <v>121.27200000000001</v>
       </c>
-      <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
       <c r="AG17" s="1"/>
       <c r="AH17" s="1"/>
@@ -2345,8 +2394,9 @@
       <c r="AU17" s="1"/>
       <c r="AV17" s="1"/>
       <c r="AW17" s="1"/>
-    </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX17" s="1"/>
+    </row>
+    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>52</v>
       </c>
@@ -2388,47 +2438,47 @@
         <v>26.2</v>
       </c>
       <c r="Q18" s="5"/>
-      <c r="R18" s="1">
+      <c r="R18" s="16"/>
+      <c r="S18" s="1">
         <f t="shared" si="4"/>
         <v>25.496183206106871</v>
       </c>
-      <c r="S18" s="1">
+      <c r="T18" s="1">
         <f t="shared" si="5"/>
         <v>25.496183206106871</v>
       </c>
-      <c r="T18" s="1">
+      <c r="U18" s="1">
         <v>30.2</v>
       </c>
-      <c r="U18" s="1">
+      <c r="V18" s="1">
         <v>41.4</v>
       </c>
-      <c r="V18" s="1">
+      <c r="W18" s="1">
         <v>58.6</v>
       </c>
-      <c r="W18" s="1">
+      <c r="X18" s="1">
         <v>46.2</v>
       </c>
-      <c r="X18" s="1">
+      <c r="Y18" s="1">
         <v>25.4</v>
       </c>
-      <c r="Y18" s="1">
+      <c r="Z18" s="1">
         <v>41.2</v>
       </c>
-      <c r="Z18" s="1">
+      <c r="AA18" s="1">
         <v>14.2</v>
       </c>
-      <c r="AA18" s="1">
+      <c r="AB18" s="1">
         <v>40.6</v>
       </c>
-      <c r="AB18" s="1">
+      <c r="AC18" s="1">
         <v>41.2</v>
       </c>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1">
-        <f>G18*Q18</f>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
       <c r="AG18" s="1"/>
       <c r="AH18" s="1"/>
@@ -2447,8 +2497,9 @@
       <c r="AU18" s="1"/>
       <c r="AV18" s="1"/>
       <c r="AW18" s="1"/>
-    </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX18" s="1"/>
+    </row>
+    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>53</v>
       </c>
@@ -2493,47 +2544,47 @@
         <f>18*P19-O19-F19</f>
         <v>49.599999999999994</v>
       </c>
-      <c r="R19" s="1">
+      <c r="R19" s="16"/>
+      <c r="S19" s="1">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="S19" s="1">
+      <c r="T19" s="1">
         <f t="shared" si="5"/>
         <v>11.951219512195124</v>
       </c>
-      <c r="T19" s="1">
+      <c r="U19" s="1">
         <v>3.4</v>
       </c>
-      <c r="U19" s="1">
+      <c r="V19" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="V19" s="1">
+      <c r="W19" s="1">
         <v>9.6</v>
       </c>
-      <c r="W19" s="1">
+      <c r="X19" s="1">
         <v>1.8</v>
       </c>
-      <c r="X19" s="1">
+      <c r="Y19" s="1">
         <v>5.8</v>
       </c>
-      <c r="Y19" s="1">
+      <c r="Z19" s="1">
         <v>7.8</v>
       </c>
-      <c r="Z19" s="1">
+      <c r="AA19" s="1">
         <v>2.8</v>
       </c>
-      <c r="AA19" s="1">
+      <c r="AB19" s="1">
         <v>6</v>
       </c>
-      <c r="AB19" s="1">
+      <c r="AC19" s="1">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1">
-        <f>G19*Q19</f>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1">
+        <f t="shared" si="6"/>
         <v>8.927999999999999</v>
       </c>
-      <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
       <c r="AG19" s="1"/>
       <c r="AH19" s="1"/>
@@ -2552,8 +2603,9 @@
       <c r="AU19" s="1"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
-    </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX19" s="1"/>
+    </row>
+    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>54</v>
       </c>
@@ -2589,22 +2641,20 @@
         <v>0</v>
       </c>
       <c r="Q20" s="11"/>
-      <c r="R20" s="9" t="e">
+      <c r="R20" s="17"/>
+      <c r="S20" s="9" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S20" s="9" t="e">
+      <c r="T20" s="9" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T20" s="9">
+      <c r="U20" s="9">
         <v>0</v>
       </c>
-      <c r="U20" s="9">
+      <c r="V20" s="9">
         <v>39.200000000000003</v>
-      </c>
-      <c r="V20" s="9">
-        <v>0</v>
       </c>
       <c r="W20" s="9">
         <v>0</v>
@@ -2624,9 +2674,11 @@
       <c r="AB20" s="9">
         <v>0</v>
       </c>
-      <c r="AC20" s="9"/>
+      <c r="AC20" s="9">
+        <v>0</v>
+      </c>
       <c r="AD20" s="9"/>
-      <c r="AE20" s="1"/>
+      <c r="AE20" s="9"/>
       <c r="AF20" s="1"/>
       <c r="AG20" s="1"/>
       <c r="AH20" s="1"/>
@@ -2645,8 +2697,9 @@
       <c r="AU20" s="1"/>
       <c r="AV20" s="1"/>
       <c r="AW20" s="1"/>
-    </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX20" s="1"/>
+    </row>
+    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>42</v>
       </c>
@@ -2687,51 +2740,53 @@
         <f t="shared" si="3"/>
         <v>26.2</v>
       </c>
-      <c r="Q21" s="5">
-        <f t="shared" ref="Q21:Q44" si="7">20*P21-O21-F21</f>
+      <c r="Q21" s="15">
+        <f t="shared" ref="Q21:Q43" si="8">20*P21-O21-F21</f>
         <v>412</v>
       </c>
-      <c r="R21" s="1">
+      <c r="R21" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="S21" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S21" s="1">
+      <c r="T21" s="1">
         <f t="shared" si="5"/>
         <v>4.2748091603053435</v>
       </c>
-      <c r="T21" s="1">
+      <c r="U21" s="1">
         <v>11.8</v>
       </c>
-      <c r="U21" s="1">
+      <c r="V21" s="1">
         <v>17.399999999999999</v>
       </c>
-      <c r="V21" s="1">
+      <c r="W21" s="1">
         <v>20</v>
       </c>
-      <c r="W21" s="1">
+      <c r="X21" s="1">
         <v>15.4</v>
       </c>
-      <c r="X21" s="1">
+      <c r="Y21" s="1">
         <v>15</v>
       </c>
-      <c r="Y21" s="1">
+      <c r="Z21" s="1">
         <v>21.6</v>
       </c>
-      <c r="Z21" s="1">
+      <c r="AA21" s="1">
         <v>20</v>
       </c>
-      <c r="AA21" s="1">
+      <c r="AB21" s="1">
         <v>13.8</v>
       </c>
-      <c r="AB21" s="1">
+      <c r="AC21" s="1">
         <v>6.2</v>
       </c>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1">
-        <f>G21*Q21</f>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1">
+        <f t="shared" ref="AE21:AE44" si="9">G21*Q21</f>
         <v>74.16</v>
       </c>
-      <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
       <c r="AG21" s="1"/>
       <c r="AH21" s="1"/>
@@ -2750,8 +2805,9 @@
       <c r="AU21" s="1"/>
       <c r="AV21" s="1"/>
       <c r="AW21" s="1"/>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX21" s="1"/>
+    </row>
+    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>56</v>
       </c>
@@ -2792,53 +2848,55 @@
         <f t="shared" si="3"/>
         <v>15.2</v>
       </c>
-      <c r="Q22" s="5">
-        <f t="shared" si="7"/>
+      <c r="Q22" s="15">
+        <f t="shared" si="8"/>
         <v>62</v>
       </c>
-      <c r="R22" s="1">
+      <c r="R22" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="S22" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S22" s="1">
+      <c r="T22" s="1">
         <f t="shared" si="5"/>
         <v>15.921052631578949</v>
       </c>
-      <c r="T22" s="1">
+      <c r="U22" s="1">
         <v>22.4</v>
       </c>
-      <c r="U22" s="1">
+      <c r="V22" s="1">
         <v>20.8</v>
-      </c>
-      <c r="V22" s="1">
-        <v>22.8</v>
       </c>
       <c r="W22" s="1">
         <v>22.8</v>
       </c>
       <c r="X22" s="1">
+        <v>22.8</v>
+      </c>
+      <c r="Y22" s="1">
         <v>20.8</v>
-      </c>
-      <c r="Y22" s="1">
-        <v>25</v>
       </c>
       <c r="Z22" s="1">
         <v>25</v>
       </c>
       <c r="AA22" s="1">
+        <v>25</v>
+      </c>
+      <c r="AB22" s="1">
         <v>19</v>
       </c>
-      <c r="AB22" s="1">
+      <c r="AC22" s="1">
         <v>4.8</v>
       </c>
-      <c r="AC22" s="12" t="s">
+      <c r="AD22" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="AD22" s="1">
-        <f>G22*Q22</f>
+      <c r="AE22" s="1">
+        <f t="shared" si="9"/>
         <v>11.16</v>
       </c>
-      <c r="AE22" s="1"/>
       <c r="AF22" s="1"/>
       <c r="AG22" s="1"/>
       <c r="AH22" s="1"/>
@@ -2857,8 +2915,9 @@
       <c r="AU22" s="1"/>
       <c r="AV22" s="1"/>
       <c r="AW22" s="1"/>
-    </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX22" s="1"/>
+    </row>
+    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>57</v>
       </c>
@@ -2898,25 +2957,23 @@
         <v>0.6</v>
       </c>
       <c r="Q23" s="5"/>
-      <c r="R23" s="1">
+      <c r="R23" s="16"/>
+      <c r="S23" s="1">
         <f t="shared" si="4"/>
         <v>35</v>
       </c>
-      <c r="S23" s="1">
+      <c r="T23" s="1">
         <f t="shared" si="5"/>
         <v>35</v>
       </c>
-      <c r="T23" s="1">
+      <c r="U23" s="1">
         <v>0.2</v>
       </c>
-      <c r="U23" s="1">
+      <c r="V23" s="1">
         <v>0</v>
       </c>
-      <c r="V23" s="1">
+      <c r="W23" s="1">
         <v>1.2</v>
-      </c>
-      <c r="W23" s="1">
-        <v>0</v>
       </c>
       <c r="X23" s="1">
         <v>0</v>
@@ -2933,14 +2990,16 @@
       <c r="AB23" s="1">
         <v>0</v>
       </c>
-      <c r="AC23" s="14" t="s">
+      <c r="AC23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AD23" s="1">
-        <f>G23*Q23</f>
+      <c r="AE23" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
       <c r="AG23" s="1"/>
       <c r="AH23" s="1"/>
@@ -2959,8 +3018,9 @@
       <c r="AU23" s="1"/>
       <c r="AV23" s="1"/>
       <c r="AW23" s="1"/>
-    </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX23" s="1"/>
+    </row>
+    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>58</v>
       </c>
@@ -3005,47 +3065,47 @@
         <f>18*P24-O24-F24</f>
         <v>29</v>
       </c>
-      <c r="R24" s="1">
+      <c r="R24" s="16"/>
+      <c r="S24" s="1">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="S24" s="1">
+      <c r="T24" s="1">
         <f t="shared" si="5"/>
         <v>13.166666666666666</v>
       </c>
-      <c r="T24" s="1">
+      <c r="U24" s="1">
         <v>1.6</v>
       </c>
-      <c r="U24" s="1">
+      <c r="V24" s="1">
         <v>1.4</v>
       </c>
-      <c r="V24" s="1">
+      <c r="W24" s="1">
         <v>3.2</v>
       </c>
-      <c r="W24" s="1">
+      <c r="X24" s="1">
         <v>1.2</v>
       </c>
-      <c r="X24" s="1">
+      <c r="Y24" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="Y24" s="1">
+      <c r="Z24" s="1">
         <v>2.4</v>
       </c>
-      <c r="Z24" s="1">
+      <c r="AA24" s="1">
         <v>1.8</v>
       </c>
-      <c r="AA24" s="1">
+      <c r="AB24" s="1">
         <v>0</v>
       </c>
-      <c r="AB24" s="1">
+      <c r="AC24" s="1">
         <v>10</v>
       </c>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1">
-        <f>G24*Q24</f>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1">
+        <f t="shared" si="9"/>
         <v>11.600000000000001</v>
       </c>
-      <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
       <c r="AG24" s="1"/>
       <c r="AH24" s="1"/>
@@ -3064,8 +3124,9 @@
       <c r="AU24" s="1"/>
       <c r="AV24" s="1"/>
       <c r="AW24" s="1"/>
-    </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX24" s="1"/>
+    </row>
+    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>59</v>
       </c>
@@ -3107,50 +3168,50 @@
         <v>4.2</v>
       </c>
       <c r="Q25" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="R25" s="1">
+      <c r="R25" s="16"/>
+      <c r="S25" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S25" s="1">
+      <c r="T25" s="1">
         <f t="shared" si="5"/>
         <v>15.952380952380953</v>
       </c>
-      <c r="T25" s="1">
+      <c r="U25" s="1">
         <v>3.4</v>
       </c>
-      <c r="U25" s="1">
+      <c r="V25" s="1">
         <v>2.6</v>
       </c>
-      <c r="V25" s="1">
+      <c r="W25" s="1">
         <v>4.4000000000000004</v>
       </c>
-      <c r="W25" s="1">
+      <c r="X25" s="1">
         <v>1.6</v>
       </c>
-      <c r="X25" s="1">
+      <c r="Y25" s="1">
         <v>1.4</v>
       </c>
-      <c r="Y25" s="1">
+      <c r="Z25" s="1">
         <v>3.2</v>
       </c>
-      <c r="Z25" s="1">
+      <c r="AA25" s="1">
         <v>3.8</v>
       </c>
-      <c r="AA25" s="1">
+      <c r="AB25" s="1">
         <v>4.8</v>
       </c>
-      <c r="AB25" s="1">
+      <c r="AC25" s="1">
         <v>7.4</v>
       </c>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1">
-        <f>G25*Q25</f>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1">
+        <f t="shared" si="9"/>
         <v>3.06</v>
       </c>
-      <c r="AE25" s="1"/>
       <c r="AF25" s="1"/>
       <c r="AG25" s="1"/>
       <c r="AH25" s="1"/>
@@ -3169,8 +3230,9 @@
       <c r="AU25" s="1"/>
       <c r="AV25" s="1"/>
       <c r="AW25" s="1"/>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX25" s="1"/>
+    </row>
+    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>60</v>
       </c>
@@ -3210,47 +3272,47 @@
         <v>7</v>
       </c>
       <c r="Q26" s="5"/>
-      <c r="R26" s="1">
+      <c r="R26" s="16"/>
+      <c r="S26" s="1">
         <f t="shared" si="4"/>
         <v>24.571428571428573</v>
       </c>
-      <c r="S26" s="1">
+      <c r="T26" s="1">
         <f t="shared" si="5"/>
         <v>24.571428571428573</v>
       </c>
-      <c r="T26" s="1">
+      <c r="U26" s="1">
         <v>6</v>
       </c>
-      <c r="U26" s="1">
+      <c r="V26" s="1">
         <v>14</v>
       </c>
-      <c r="V26" s="1">
+      <c r="W26" s="1">
         <v>7.2</v>
       </c>
-      <c r="W26" s="1">
+      <c r="X26" s="1">
         <v>4.8</v>
-      </c>
-      <c r="X26" s="1">
-        <v>8.8000000000000007</v>
       </c>
       <c r="Y26" s="1">
         <v>8.8000000000000007</v>
       </c>
       <c r="Z26" s="1">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="AA26" s="1">
         <v>6.2</v>
       </c>
-      <c r="AA26" s="1">
+      <c r="AB26" s="1">
         <v>0.4</v>
       </c>
-      <c r="AB26" s="1">
+      <c r="AC26" s="1">
         <v>9.1999999999999993</v>
       </c>
-      <c r="AC26" s="1"/>
-      <c r="AD26" s="1">
-        <f>G26*Q26</f>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
       <c r="AG26" s="1"/>
       <c r="AH26" s="1"/>
@@ -3269,8 +3331,9 @@
       <c r="AU26" s="1"/>
       <c r="AV26" s="1"/>
       <c r="AW26" s="1"/>
-    </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX26" s="1"/>
+    </row>
+    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>61</v>
       </c>
@@ -3314,50 +3377,50 @@
         <v>31.4</v>
       </c>
       <c r="Q27" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>228</v>
       </c>
-      <c r="R27" s="1">
+      <c r="R27" s="16"/>
+      <c r="S27" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S27" s="1">
+      <c r="T27" s="1">
         <f t="shared" si="5"/>
         <v>12.738853503184714</v>
       </c>
-      <c r="T27" s="1">
+      <c r="U27" s="1">
         <v>28.2</v>
       </c>
-      <c r="U27" s="1">
+      <c r="V27" s="1">
         <v>30.4</v>
       </c>
-      <c r="V27" s="1">
+      <c r="W27" s="1">
         <v>20.8</v>
       </c>
-      <c r="W27" s="1">
+      <c r="X27" s="1">
         <v>18.2</v>
       </c>
-      <c r="X27" s="1">
+      <c r="Y27" s="1">
         <v>23.8</v>
       </c>
-      <c r="Y27" s="1">
+      <c r="Z27" s="1">
         <v>13</v>
       </c>
-      <c r="Z27" s="1">
+      <c r="AA27" s="1">
         <v>27.6</v>
       </c>
-      <c r="AA27" s="1">
+      <c r="AB27" s="1">
         <v>27.2</v>
       </c>
-      <c r="AB27" s="1">
+      <c r="AC27" s="1">
         <v>19</v>
       </c>
-      <c r="AC27" s="1"/>
-      <c r="AD27" s="1">
-        <f>G27*Q27</f>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1">
+        <f t="shared" si="9"/>
         <v>41.04</v>
       </c>
-      <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
       <c r="AG27" s="1"/>
       <c r="AH27" s="1"/>
@@ -3376,8 +3439,9 @@
       <c r="AU27" s="1"/>
       <c r="AV27" s="1"/>
       <c r="AW27" s="1"/>
-    </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX27" s="1"/>
+    </row>
+    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>62</v>
       </c>
@@ -3421,50 +3485,50 @@
         <v>19</v>
       </c>
       <c r="Q28" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>84</v>
       </c>
-      <c r="R28" s="1">
+      <c r="R28" s="16"/>
+      <c r="S28" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S28" s="1">
+      <c r="T28" s="1">
         <f t="shared" si="5"/>
         <v>15.578947368421053</v>
       </c>
-      <c r="T28" s="1">
+      <c r="U28" s="1">
         <v>19.399999999999999</v>
       </c>
-      <c r="U28" s="1">
+      <c r="V28" s="1">
         <v>25</v>
       </c>
-      <c r="V28" s="1">
+      <c r="W28" s="1">
         <v>20.2</v>
       </c>
-      <c r="W28" s="1">
+      <c r="X28" s="1">
         <v>19.600000000000001</v>
       </c>
-      <c r="X28" s="1">
+      <c r="Y28" s="1">
         <v>25.6</v>
       </c>
-      <c r="Y28" s="1">
+      <c r="Z28" s="1">
         <v>19.399999999999999</v>
       </c>
-      <c r="Z28" s="1">
+      <c r="AA28" s="1">
         <v>23.4</v>
       </c>
-      <c r="AA28" s="1">
+      <c r="AB28" s="1">
         <v>29.6</v>
       </c>
-      <c r="AB28" s="1">
+      <c r="AC28" s="1">
         <v>23.2</v>
       </c>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1">
-        <f>G28*Q28</f>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1">
+        <f t="shared" si="9"/>
         <v>15.12</v>
       </c>
-      <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
       <c r="AG28" s="1"/>
       <c r="AH28" s="1"/>
@@ -3483,8 +3547,9 @@
       <c r="AU28" s="1"/>
       <c r="AV28" s="1"/>
       <c r="AW28" s="1"/>
-    </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX28" s="1"/>
+    </row>
+    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>63</v>
       </c>
@@ -3524,50 +3589,50 @@
         <v>9.4</v>
       </c>
       <c r="Q29" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>49</v>
       </c>
-      <c r="R29" s="1">
+      <c r="R29" s="16"/>
+      <c r="S29" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S29" s="1">
+      <c r="T29" s="1">
         <f t="shared" si="5"/>
         <v>14.787234042553191</v>
       </c>
-      <c r="T29" s="1">
+      <c r="U29" s="1">
         <v>9.4</v>
       </c>
-      <c r="U29" s="1">
+      <c r="V29" s="1">
         <v>8</v>
       </c>
-      <c r="V29" s="1">
+      <c r="W29" s="1">
         <v>7.4</v>
       </c>
-      <c r="W29" s="1">
+      <c r="X29" s="1">
         <v>9</v>
       </c>
-      <c r="X29" s="1">
+      <c r="Y29" s="1">
         <v>8.6</v>
       </c>
-      <c r="Y29" s="1">
+      <c r="Z29" s="1">
         <v>11.8</v>
       </c>
-      <c r="Z29" s="1">
+      <c r="AA29" s="1">
         <v>9.6</v>
       </c>
-      <c r="AA29" s="1">
+      <c r="AB29" s="1">
         <v>15.2</v>
       </c>
-      <c r="AB29" s="1">
+      <c r="AC29" s="1">
         <v>13.2</v>
       </c>
-      <c r="AC29" s="1"/>
-      <c r="AD29" s="1">
-        <f>G29*Q29</f>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1">
+        <f t="shared" si="9"/>
         <v>8.82</v>
       </c>
-      <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
       <c r="AG29" s="1"/>
       <c r="AH29" s="1"/>
@@ -3586,8 +3651,9 @@
       <c r="AU29" s="1"/>
       <c r="AV29" s="1"/>
       <c r="AW29" s="1"/>
-    </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX29" s="1"/>
+    </row>
+    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>64</v>
       </c>
@@ -3629,50 +3695,50 @@
         <v>6.6</v>
       </c>
       <c r="Q30" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
-      <c r="R30" s="1">
+      <c r="R30" s="16"/>
+      <c r="S30" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S30" s="1">
+      <c r="T30" s="1">
         <f t="shared" si="5"/>
         <v>15.151515151515152</v>
       </c>
-      <c r="T30" s="1">
+      <c r="U30" s="1">
         <v>6.8</v>
       </c>
-      <c r="U30" s="1">
+      <c r="V30" s="1">
         <v>7.8</v>
       </c>
-      <c r="V30" s="1">
+      <c r="W30" s="1">
         <v>9.4</v>
       </c>
-      <c r="W30" s="1">
+      <c r="X30" s="1">
         <v>7.8</v>
       </c>
-      <c r="X30" s="1">
+      <c r="Y30" s="1">
         <v>7.2</v>
       </c>
-      <c r="Y30" s="1">
+      <c r="Z30" s="1">
         <v>9</v>
       </c>
-      <c r="Z30" s="1">
+      <c r="AA30" s="1">
         <v>9.8000000000000007</v>
       </c>
-      <c r="AA30" s="1">
+      <c r="AB30" s="1">
         <v>6.2</v>
       </c>
-      <c r="AB30" s="1">
+      <c r="AC30" s="1">
         <v>0</v>
       </c>
-      <c r="AC30" s="1"/>
-      <c r="AD30" s="1">
-        <f>G30*Q30</f>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1">
+        <f t="shared" si="9"/>
         <v>5.76</v>
       </c>
-      <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
       <c r="AG30" s="1"/>
       <c r="AH30" s="1"/>
@@ -3691,8 +3757,9 @@
       <c r="AU30" s="1"/>
       <c r="AV30" s="1"/>
       <c r="AW30" s="1"/>
-    </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX30" s="1"/>
+    </row>
+    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>65</v>
       </c>
@@ -3736,50 +3803,50 @@
         <v>26.2</v>
       </c>
       <c r="Q31" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>127</v>
       </c>
-      <c r="R31" s="1">
+      <c r="R31" s="16"/>
+      <c r="S31" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S31" s="1">
+      <c r="T31" s="1">
         <f t="shared" si="5"/>
         <v>15.152671755725191</v>
       </c>
-      <c r="T31" s="1">
+      <c r="U31" s="1">
         <v>26.6</v>
       </c>
-      <c r="U31" s="1">
+      <c r="V31" s="1">
         <v>32.6</v>
       </c>
-      <c r="V31" s="1">
+      <c r="W31" s="1">
         <v>15.6</v>
       </c>
-      <c r="W31" s="1">
+      <c r="X31" s="1">
         <v>24.6</v>
       </c>
-      <c r="X31" s="1">
+      <c r="Y31" s="1">
         <v>27.4</v>
       </c>
-      <c r="Y31" s="1">
+      <c r="Z31" s="1">
         <v>25.4</v>
       </c>
-      <c r="Z31" s="1">
+      <c r="AA31" s="1">
         <v>20.8</v>
       </c>
-      <c r="AA31" s="1">
+      <c r="AB31" s="1">
         <v>24.6</v>
       </c>
-      <c r="AB31" s="1">
+      <c r="AC31" s="1">
         <v>32.4</v>
       </c>
-      <c r="AC31" s="1"/>
-      <c r="AD31" s="1">
-        <f>G31*Q31</f>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1">
+        <f t="shared" si="9"/>
         <v>22.86</v>
       </c>
-      <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
       <c r="AG31" s="1"/>
       <c r="AH31" s="1"/>
@@ -3798,8 +3865,9 @@
       <c r="AU31" s="1"/>
       <c r="AV31" s="1"/>
       <c r="AW31" s="1"/>
-    </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX31" s="1"/>
+    </row>
+    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>66</v>
       </c>
@@ -3841,50 +3909,50 @@
         <v>19.600000000000001</v>
       </c>
       <c r="Q32" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>270</v>
       </c>
-      <c r="R32" s="1">
+      <c r="R32" s="16"/>
+      <c r="S32" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S32" s="1">
+      <c r="T32" s="1">
         <f t="shared" si="5"/>
         <v>6.2244897959183669</v>
       </c>
-      <c r="T32" s="1">
+      <c r="U32" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="U32" s="1">
+      <c r="V32" s="1">
         <v>14</v>
       </c>
-      <c r="V32" s="1">
+      <c r="W32" s="1">
         <v>12.4</v>
       </c>
-      <c r="W32" s="1">
+      <c r="X32" s="1">
         <v>10.8</v>
       </c>
-      <c r="X32" s="1">
+      <c r="Y32" s="1">
         <v>11.6</v>
       </c>
-      <c r="Y32" s="1">
+      <c r="Z32" s="1">
         <v>9.4</v>
       </c>
-      <c r="Z32" s="1">
+      <c r="AA32" s="1">
         <v>13.2</v>
       </c>
-      <c r="AA32" s="1">
+      <c r="AB32" s="1">
         <v>12.8</v>
       </c>
-      <c r="AB32" s="1">
+      <c r="AC32" s="1">
         <v>4.8</v>
       </c>
-      <c r="AC32" s="1"/>
-      <c r="AD32" s="1">
-        <f>G32*Q32</f>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1">
+        <f t="shared" si="9"/>
         <v>48.6</v>
       </c>
-      <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
       <c r="AG32" s="1"/>
       <c r="AH32" s="1"/>
@@ -3903,8 +3971,9 @@
       <c r="AU32" s="1"/>
       <c r="AV32" s="1"/>
       <c r="AW32" s="1"/>
-    </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX32" s="1"/>
+    </row>
+    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
@@ -3938,17 +4007,15 @@
         <v>0</v>
       </c>
       <c r="Q33" s="5"/>
-      <c r="R33" s="1" t="e">
+      <c r="R33" s="16"/>
+      <c r="S33" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S33" s="1" t="e">
+      <c r="T33" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T33" s="1">
-        <v>0</v>
-      </c>
       <c r="U33" s="1">
         <v>0</v>
       </c>
@@ -3973,14 +4040,16 @@
       <c r="AB33" s="1">
         <v>0</v>
       </c>
-      <c r="AC33" s="14" t="s">
+      <c r="AC33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AD33" s="1">
-        <f>G33*Q33</f>
+      <c r="AE33" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
       <c r="AG33" s="1"/>
       <c r="AH33" s="1"/>
@@ -3999,8 +4068,9 @@
       <c r="AU33" s="1"/>
       <c r="AV33" s="1"/>
       <c r="AW33" s="1"/>
-    </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX33" s="1"/>
+    </row>
+    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>68</v>
       </c>
@@ -4038,47 +4108,47 @@
         <v>6.4</v>
       </c>
       <c r="Q34" s="5"/>
-      <c r="R34" s="1">
+      <c r="R34" s="16"/>
+      <c r="S34" s="1">
         <f t="shared" si="4"/>
         <v>17.96875</v>
       </c>
-      <c r="S34" s="1">
+      <c r="T34" s="1">
         <f t="shared" si="5"/>
         <v>17.96875</v>
       </c>
-      <c r="T34" s="1">
+      <c r="U34" s="1">
         <v>2.4</v>
       </c>
-      <c r="U34" s="1">
+      <c r="V34" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="V34" s="1">
+      <c r="W34" s="1">
         <v>9.1999999999999993</v>
       </c>
-      <c r="W34" s="1">
+      <c r="X34" s="1">
         <v>3</v>
       </c>
-      <c r="X34" s="1">
+      <c r="Y34" s="1">
         <v>6.2</v>
-      </c>
-      <c r="Y34" s="1">
-        <v>7</v>
       </c>
       <c r="Z34" s="1">
         <v>7</v>
       </c>
       <c r="AA34" s="1">
+        <v>7</v>
+      </c>
+      <c r="AB34" s="1">
         <v>3.6</v>
       </c>
-      <c r="AB34" s="1">
+      <c r="AC34" s="1">
         <v>1</v>
       </c>
-      <c r="AC34" s="1"/>
-      <c r="AD34" s="1">
-        <f>G34*Q34</f>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
       <c r="AG34" s="1"/>
       <c r="AH34" s="1"/>
@@ -4097,8 +4167,9 @@
       <c r="AU34" s="1"/>
       <c r="AV34" s="1"/>
       <c r="AW34" s="1"/>
-    </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX34" s="1"/>
+    </row>
+    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -4138,50 +4209,50 @@
         <v>8.4</v>
       </c>
       <c r="Q35" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>78</v>
       </c>
-      <c r="R35" s="1">
+      <c r="R35" s="16"/>
+      <c r="S35" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S35" s="1">
+      <c r="T35" s="1">
         <f t="shared" si="5"/>
         <v>10.714285714285714</v>
       </c>
-      <c r="T35" s="1">
+      <c r="U35" s="1">
         <v>6.2</v>
       </c>
-      <c r="U35" s="1">
+      <c r="V35" s="1">
         <v>2.4</v>
       </c>
-      <c r="V35" s="1">
+      <c r="W35" s="1">
         <v>9.8000000000000007</v>
       </c>
-      <c r="W35" s="1">
+      <c r="X35" s="1">
         <v>2.2000000000000002</v>
       </c>
-      <c r="X35" s="1">
+      <c r="Y35" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="Y35" s="1">
+      <c r="Z35" s="1">
         <v>8.6</v>
       </c>
-      <c r="Z35" s="1">
+      <c r="AA35" s="1">
         <v>7.4</v>
       </c>
-      <c r="AA35" s="1">
+      <c r="AB35" s="1">
         <v>5.8</v>
       </c>
-      <c r="AB35" s="1">
+      <c r="AC35" s="1">
         <v>12.4</v>
       </c>
-      <c r="AC35" s="1"/>
-      <c r="AD35" s="1">
-        <f>G35*Q35</f>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1">
+        <f t="shared" si="9"/>
         <v>14.04</v>
       </c>
-      <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
       <c r="AG35" s="1"/>
       <c r="AH35" s="1"/>
@@ -4200,8 +4271,9 @@
       <c r="AU35" s="1"/>
       <c r="AV35" s="1"/>
       <c r="AW35" s="1"/>
-    </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX35" s="1"/>
+    </row>
+    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
@@ -4237,49 +4309,49 @@
         <v>0</v>
       </c>
       <c r="Q36" s="5"/>
-      <c r="R36" s="1" t="e">
+      <c r="R36" s="16"/>
+      <c r="S36" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S36" s="1" t="e">
+      <c r="T36" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T36" s="1">
+      <c r="U36" s="1">
         <v>1.4072</v>
       </c>
-      <c r="U36" s="1">
+      <c r="V36" s="1">
         <v>1.3271999999999999</v>
       </c>
-      <c r="V36" s="1">
+      <c r="W36" s="1">
         <v>1.9408000000000001</v>
       </c>
-      <c r="W36" s="1">
+      <c r="X36" s="1">
         <v>0.68840000000000001</v>
       </c>
-      <c r="X36" s="1">
+      <c r="Y36" s="1">
         <v>1.3236000000000001</v>
       </c>
-      <c r="Y36" s="1">
+      <c r="Z36" s="1">
         <v>0.68840000000000001</v>
       </c>
-      <c r="Z36" s="1">
+      <c r="AA36" s="1">
         <v>2.0207999999999999</v>
       </c>
-      <c r="AA36" s="1">
+      <c r="AB36" s="1">
         <v>1.988</v>
       </c>
-      <c r="AB36" s="1">
+      <c r="AC36" s="1">
         <v>1.3355999999999999</v>
       </c>
-      <c r="AC36" s="14" t="s">
+      <c r="AD36" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AD36" s="1">
-        <f>G36*Q36</f>
+      <c r="AE36" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1"/>
       <c r="AH36" s="1"/>
@@ -4298,8 +4370,9 @@
       <c r="AU36" s="1"/>
       <c r="AV36" s="1"/>
       <c r="AW36" s="1"/>
-    </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX36" s="1"/>
+    </row>
+    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>71</v>
       </c>
@@ -4341,50 +4414,50 @@
         <v>3.0844</v>
       </c>
       <c r="Q37" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>10.238</v>
       </c>
-      <c r="R37" s="1">
+      <c r="R37" s="16"/>
+      <c r="S37" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S37" s="1">
+      <c r="T37" s="1">
         <f t="shared" si="5"/>
         <v>16.680715860459085</v>
       </c>
-      <c r="T37" s="1">
+      <c r="U37" s="1">
         <v>3.2427999999999999</v>
       </c>
-      <c r="U37" s="1">
+      <c r="V37" s="1">
         <v>4.4512</v>
       </c>
-      <c r="V37" s="1">
+      <c r="W37" s="1">
         <v>4.6284000000000001</v>
       </c>
-      <c r="W37" s="1">
+      <c r="X37" s="1">
         <v>2.6107999999999998</v>
       </c>
-      <c r="X37" s="1">
+      <c r="Y37" s="1">
         <v>3.7959999999999998</v>
       </c>
-      <c r="Y37" s="1">
+      <c r="Z37" s="1">
         <v>0</v>
       </c>
-      <c r="Z37" s="1">
+      <c r="AA37" s="1">
         <v>0.71599999999999997</v>
       </c>
-      <c r="AA37" s="1">
+      <c r="AB37" s="1">
         <v>3.9607999999999999</v>
       </c>
-      <c r="AB37" s="1">
+      <c r="AC37" s="1">
         <v>3.8763999999999998</v>
       </c>
-      <c r="AC37" s="1"/>
-      <c r="AD37" s="1">
-        <f>G37*Q37</f>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1">
+        <f t="shared" si="9"/>
         <v>10.238</v>
       </c>
-      <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
       <c r="AG37" s="1"/>
       <c r="AH37" s="1"/>
@@ -4403,8 +4476,9 @@
       <c r="AU37" s="1"/>
       <c r="AV37" s="1"/>
       <c r="AW37" s="1"/>
-    </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX37" s="1"/>
+    </row>
+    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>72</v>
       </c>
@@ -4442,47 +4516,47 @@
         <v>1.4</v>
       </c>
       <c r="Q38" s="5"/>
-      <c r="R38" s="1">
+      <c r="R38" s="16"/>
+      <c r="S38" s="1">
         <f t="shared" si="4"/>
         <v>55</v>
       </c>
-      <c r="S38" s="1">
+      <c r="T38" s="1">
         <f t="shared" si="5"/>
         <v>55</v>
       </c>
-      <c r="T38" s="1">
+      <c r="U38" s="1">
         <v>0</v>
-      </c>
-      <c r="U38" s="1">
-        <v>-0.2</v>
       </c>
       <c r="V38" s="1">
         <v>-0.2</v>
       </c>
       <c r="W38" s="1">
+        <v>-0.2</v>
+      </c>
+      <c r="X38" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="X38" s="1">
+      <c r="Y38" s="1">
         <v>13.6</v>
       </c>
-      <c r="Y38" s="1">
+      <c r="Z38" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="Z38" s="1">
+      <c r="AA38" s="1">
         <v>4.8</v>
       </c>
-      <c r="AA38" s="1">
+      <c r="AB38" s="1">
         <v>-0.4</v>
       </c>
-      <c r="AB38" s="1">
+      <c r="AC38" s="1">
         <v>8.6</v>
       </c>
-      <c r="AC38" s="1"/>
-      <c r="AD38" s="1">
-        <f>G38*Q38</f>
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
       <c r="AG38" s="1"/>
       <c r="AH38" s="1"/>
@@ -4501,8 +4575,9 @@
       <c r="AU38" s="1"/>
       <c r="AV38" s="1"/>
       <c r="AW38" s="1"/>
-    </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX38" s="1"/>
+    </row>
+    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>73</v>
       </c>
@@ -4544,47 +4619,47 @@
         <v>8.4</v>
       </c>
       <c r="Q39" s="5"/>
-      <c r="R39" s="1">
+      <c r="R39" s="16"/>
+      <c r="S39" s="1">
         <f t="shared" si="4"/>
         <v>22.5</v>
       </c>
-      <c r="S39" s="1">
+      <c r="T39" s="1">
         <f t="shared" si="5"/>
         <v>22.5</v>
       </c>
-      <c r="T39" s="1">
+      <c r="U39" s="1">
         <v>11</v>
       </c>
-      <c r="U39" s="1">
+      <c r="V39" s="1">
         <v>9.1999999999999993</v>
       </c>
-      <c r="V39" s="1">
+      <c r="W39" s="1">
         <v>8.4</v>
       </c>
-      <c r="W39" s="1">
+      <c r="X39" s="1">
         <v>7</v>
       </c>
-      <c r="X39" s="1">
+      <c r="Y39" s="1">
         <v>14.2</v>
       </c>
-      <c r="Y39" s="1">
+      <c r="Z39" s="1">
         <v>7.6</v>
       </c>
-      <c r="Z39" s="1">
+      <c r="AA39" s="1">
         <v>7.4</v>
       </c>
-      <c r="AA39" s="1">
+      <c r="AB39" s="1">
         <v>2.6</v>
       </c>
-      <c r="AB39" s="1">
+      <c r="AC39" s="1">
         <v>12.6</v>
       </c>
-      <c r="AC39" s="1"/>
-      <c r="AD39" s="1">
-        <f>G39*Q39</f>
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
       <c r="AG39" s="1"/>
       <c r="AH39" s="1"/>
@@ -4603,8 +4678,9 @@
       <c r="AU39" s="1"/>
       <c r="AV39" s="1"/>
       <c r="AW39" s="1"/>
-    </row>
-    <row r="40" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX39" s="1"/>
+    </row>
+    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>74</v>
       </c>
@@ -4644,49 +4720,49 @@
         <v>5</v>
       </c>
       <c r="Q40" s="5"/>
-      <c r="R40" s="1">
+      <c r="R40" s="16"/>
+      <c r="S40" s="1">
         <f t="shared" si="4"/>
         <v>29.2</v>
       </c>
-      <c r="S40" s="1">
+      <c r="T40" s="1">
         <f t="shared" si="5"/>
         <v>29.2</v>
       </c>
-      <c r="T40" s="1">
-        <v>3.6</v>
-      </c>
       <c r="U40" s="1">
         <v>3.6</v>
       </c>
       <c r="V40" s="1">
+        <v>3.6</v>
+      </c>
+      <c r="W40" s="1">
         <v>10</v>
       </c>
-      <c r="W40" s="1">
+      <c r="X40" s="1">
         <v>4</v>
       </c>
-      <c r="X40" s="1">
+      <c r="Y40" s="1">
         <v>8</v>
       </c>
-      <c r="Y40" s="1">
+      <c r="Z40" s="1">
         <v>7.6</v>
-      </c>
-      <c r="Z40" s="1">
-        <v>7.4</v>
       </c>
       <c r="AA40" s="1">
         <v>7.4</v>
       </c>
       <c r="AB40" s="1">
+        <v>7.4</v>
+      </c>
+      <c r="AC40" s="1">
         <v>5.2</v>
       </c>
-      <c r="AC40" s="14" t="s">
+      <c r="AD40" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AD40" s="1">
-        <f>G40*Q40</f>
+      <c r="AE40" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
       <c r="AG40" s="1"/>
       <c r="AH40" s="1"/>
@@ -4705,8 +4781,9 @@
       <c r="AU40" s="1"/>
       <c r="AV40" s="1"/>
       <c r="AW40" s="1"/>
-    </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX40" s="1"/>
+    </row>
+    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>75</v>
       </c>
@@ -4748,50 +4825,50 @@
         <v>38.799999999999997</v>
       </c>
       <c r="Q41" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>582</v>
       </c>
-      <c r="R41" s="1">
+      <c r="R41" s="16"/>
+      <c r="S41" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S41" s="1">
+      <c r="T41" s="1">
         <f t="shared" si="5"/>
         <v>5</v>
       </c>
-      <c r="T41" s="1">
+      <c r="U41" s="1">
         <v>18.600000000000001</v>
       </c>
-      <c r="U41" s="1">
+      <c r="V41" s="1">
         <v>21.8</v>
       </c>
-      <c r="V41" s="1">
+      <c r="W41" s="1">
         <v>28</v>
       </c>
-      <c r="W41" s="1">
+      <c r="X41" s="1">
         <v>12</v>
       </c>
-      <c r="X41" s="1">
+      <c r="Y41" s="1">
         <v>24.6</v>
       </c>
-      <c r="Y41" s="1">
+      <c r="Z41" s="1">
         <v>13.2</v>
       </c>
-      <c r="Z41" s="1">
+      <c r="AA41" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="AA41" s="1">
+      <c r="AB41" s="1">
         <v>13.8</v>
       </c>
-      <c r="AB41" s="1">
+      <c r="AC41" s="1">
         <v>31.8</v>
       </c>
-      <c r="AC41" s="1"/>
-      <c r="AD41" s="1">
-        <f>G41*Q41</f>
+      <c r="AD41" s="1"/>
+      <c r="AE41" s="1">
+        <f t="shared" si="9"/>
         <v>116.4</v>
       </c>
-      <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
       <c r="AG41" s="1"/>
       <c r="AH41" s="1"/>
@@ -4810,8 +4887,9 @@
       <c r="AU41" s="1"/>
       <c r="AV41" s="1"/>
       <c r="AW41" s="1"/>
-    </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX41" s="1"/>
+    </row>
+    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>76</v>
       </c>
@@ -4852,47 +4930,47 @@
         <f>18*P42-O42-F42</f>
         <v>28.029599999999995</v>
       </c>
-      <c r="R42" s="1">
+      <c r="R42" s="16"/>
+      <c r="S42" s="1">
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-      <c r="S42" s="1">
+      <c r="T42" s="1">
         <f t="shared" si="5"/>
         <v>10.649323402916187</v>
       </c>
-      <c r="T42" s="1">
+      <c r="U42" s="1">
         <v>1.9352</v>
       </c>
-      <c r="U42" s="1">
+      <c r="V42" s="1">
         <v>2.5895999999999999</v>
       </c>
-      <c r="V42" s="1">
+      <c r="W42" s="1">
         <v>3.7652000000000001</v>
       </c>
-      <c r="W42" s="1">
+      <c r="X42" s="1">
         <v>3.7711999999999999</v>
       </c>
-      <c r="X42" s="1">
+      <c r="Y42" s="1">
         <v>3.0623999999999998</v>
       </c>
-      <c r="Y42" s="1">
+      <c r="Z42" s="1">
         <v>3.6636000000000002</v>
       </c>
-      <c r="Z42" s="1">
+      <c r="AA42" s="1">
         <v>7.4767999999999999</v>
       </c>
-      <c r="AA42" s="1">
+      <c r="AB42" s="1">
         <v>1.1104000000000001</v>
       </c>
-      <c r="AB42" s="1">
+      <c r="AC42" s="1">
         <v>3.8748</v>
       </c>
-      <c r="AC42" s="1"/>
-      <c r="AD42" s="1">
-        <f>G42*Q42</f>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1">
+        <f t="shared" si="9"/>
         <v>28.029599999999995</v>
       </c>
-      <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
       <c r="AG42" s="1"/>
       <c r="AH42" s="1"/>
@@ -4911,8 +4989,9 @@
       <c r="AU42" s="1"/>
       <c r="AV42" s="1"/>
       <c r="AW42" s="1"/>
-    </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX42" s="1"/>
+    </row>
+    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>77</v>
       </c>
@@ -4954,50 +5033,50 @@
         <v>29.4</v>
       </c>
       <c r="Q43" s="5">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>463</v>
       </c>
-      <c r="R43" s="1">
+      <c r="R43" s="16"/>
+      <c r="S43" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="S43" s="1">
+      <c r="T43" s="1">
         <f t="shared" si="5"/>
         <v>4.2517006802721093</v>
       </c>
-      <c r="T43" s="1">
+      <c r="U43" s="1">
         <v>13.4</v>
       </c>
-      <c r="U43" s="1">
+      <c r="V43" s="1">
         <v>11</v>
       </c>
-      <c r="V43" s="1">
+      <c r="W43" s="1">
         <v>17.600000000000001</v>
       </c>
-      <c r="W43" s="1">
+      <c r="X43" s="1">
         <v>10.6</v>
       </c>
-      <c r="X43" s="1">
+      <c r="Y43" s="1">
         <v>15</v>
       </c>
-      <c r="Y43" s="1">
+      <c r="Z43" s="1">
         <v>8.6</v>
       </c>
-      <c r="Z43" s="1">
+      <c r="AA43" s="1">
         <v>12.2</v>
       </c>
-      <c r="AA43" s="1">
+      <c r="AB43" s="1">
         <v>14</v>
       </c>
-      <c r="AB43" s="1">
+      <c r="AC43" s="1">
         <v>18.600000000000001</v>
       </c>
-      <c r="AC43" s="1"/>
-      <c r="AD43" s="1">
-        <f>G43*Q43</f>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1">
+        <f t="shared" si="9"/>
         <v>92.600000000000009</v>
       </c>
-      <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
       <c r="AG43" s="1"/>
       <c r="AH43" s="1"/>
@@ -5016,8 +5095,9 @@
       <c r="AU43" s="1"/>
       <c r="AV43" s="1"/>
       <c r="AW43" s="1"/>
-    </row>
-    <row r="44" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX43" s="1"/>
+    </row>
+    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>78</v>
       </c>
@@ -5057,49 +5137,49 @@
         <v>1.4996</v>
       </c>
       <c r="Q44" s="5"/>
-      <c r="R44" s="1">
+      <c r="R44" s="16"/>
+      <c r="S44" s="1">
         <f t="shared" si="4"/>
         <v>125.02534009069085</v>
       </c>
-      <c r="S44" s="1">
+      <c r="T44" s="1">
         <f t="shared" si="5"/>
         <v>125.02534009069085</v>
       </c>
-      <c r="T44" s="1">
+      <c r="U44" s="1">
         <v>2.1772</v>
       </c>
-      <c r="U44" s="1">
+      <c r="V44" s="1">
         <v>1.4212</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
       </c>
       <c r="W44" s="1">
         <v>0</v>
       </c>
       <c r="X44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="1">
         <v>2.9496000000000002</v>
       </c>
-      <c r="Y44" s="1">
+      <c r="Z44" s="1">
         <v>2.4E-2</v>
       </c>
-      <c r="Z44" s="1">
+      <c r="AA44" s="1">
         <v>2.1876000000000002</v>
       </c>
-      <c r="AA44" s="1">
+      <c r="AB44" s="1">
         <v>8.5687999999999995</v>
       </c>
-      <c r="AB44" s="1">
+      <c r="AC44" s="1">
         <v>1.4568000000000001</v>
       </c>
-      <c r="AC44" s="14" t="s">
+      <c r="AD44" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="AD44" s="1">
-        <f>G44*Q44</f>
+      <c r="AE44" s="1">
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
       <c r="AG44" s="1"/>
       <c r="AH44" s="1"/>
@@ -5118,8 +5198,9 @@
       <c r="AU44" s="1"/>
       <c r="AV44" s="1"/>
       <c r="AW44" s="1"/>
-    </row>
-    <row r="45" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX44" s="1"/>
+    </row>
+    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -5169,8 +5250,9 @@
       <c r="AU45" s="1"/>
       <c r="AV45" s="1"/>
       <c r="AW45" s="1"/>
-    </row>
-    <row r="46" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX45" s="1"/>
+    </row>
+    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -5220,8 +5302,9 @@
       <c r="AU46" s="1"/>
       <c r="AV46" s="1"/>
       <c r="AW46" s="1"/>
-    </row>
-    <row r="47" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX46" s="1"/>
+    </row>
+    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -5271,8 +5354,9 @@
       <c r="AU47" s="1"/>
       <c r="AV47" s="1"/>
       <c r="AW47" s="1"/>
-    </row>
-    <row r="48" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX47" s="1"/>
+    </row>
+    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -5322,8 +5406,9 @@
       <c r="AU48" s="1"/>
       <c r="AV48" s="1"/>
       <c r="AW48" s="1"/>
-    </row>
-    <row r="49" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX48" s="1"/>
+    </row>
+    <row r="49" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -5373,8 +5458,9 @@
       <c r="AU49" s="1"/>
       <c r="AV49" s="1"/>
       <c r="AW49" s="1"/>
-    </row>
-    <row r="50" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX49" s="1"/>
+    </row>
+    <row r="50" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -5424,8 +5510,9 @@
       <c r="AU50" s="1"/>
       <c r="AV50" s="1"/>
       <c r="AW50" s="1"/>
-    </row>
-    <row r="51" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX50" s="1"/>
+    </row>
+    <row r="51" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -5475,8 +5562,9 @@
       <c r="AU51" s="1"/>
       <c r="AV51" s="1"/>
       <c r="AW51" s="1"/>
-    </row>
-    <row r="52" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX51" s="1"/>
+    </row>
+    <row r="52" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -5526,8 +5614,9 @@
       <c r="AU52" s="1"/>
       <c r="AV52" s="1"/>
       <c r="AW52" s="1"/>
-    </row>
-    <row r="53" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX52" s="1"/>
+    </row>
+    <row r="53" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -5577,8 +5666,9 @@
       <c r="AU53" s="1"/>
       <c r="AV53" s="1"/>
       <c r="AW53" s="1"/>
-    </row>
-    <row r="54" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX53" s="1"/>
+    </row>
+    <row r="54" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -5628,8 +5718,9 @@
       <c r="AU54" s="1"/>
       <c r="AV54" s="1"/>
       <c r="AW54" s="1"/>
-    </row>
-    <row r="55" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX54" s="1"/>
+    </row>
+    <row r="55" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -5679,8 +5770,9 @@
       <c r="AU55" s="1"/>
       <c r="AV55" s="1"/>
       <c r="AW55" s="1"/>
-    </row>
-    <row r="56" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX55" s="1"/>
+    </row>
+    <row r="56" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -5730,8 +5822,9 @@
       <c r="AU56" s="1"/>
       <c r="AV56" s="1"/>
       <c r="AW56" s="1"/>
-    </row>
-    <row r="57" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX56" s="1"/>
+    </row>
+    <row r="57" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -5781,8 +5874,9 @@
       <c r="AU57" s="1"/>
       <c r="AV57" s="1"/>
       <c r="AW57" s="1"/>
-    </row>
-    <row r="58" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX57" s="1"/>
+    </row>
+    <row r="58" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -5832,8 +5926,9 @@
       <c r="AU58" s="1"/>
       <c r="AV58" s="1"/>
       <c r="AW58" s="1"/>
-    </row>
-    <row r="59" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX58" s="1"/>
+    </row>
+    <row r="59" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -5883,8 +5978,9 @@
       <c r="AU59" s="1"/>
       <c r="AV59" s="1"/>
       <c r="AW59" s="1"/>
-    </row>
-    <row r="60" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX59" s="1"/>
+    </row>
+    <row r="60" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -5934,8 +6030,9 @@
       <c r="AU60" s="1"/>
       <c r="AV60" s="1"/>
       <c r="AW60" s="1"/>
-    </row>
-    <row r="61" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX60" s="1"/>
+    </row>
+    <row r="61" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -5985,8 +6082,9 @@
       <c r="AU61" s="1"/>
       <c r="AV61" s="1"/>
       <c r="AW61" s="1"/>
-    </row>
-    <row r="62" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX61" s="1"/>
+    </row>
+    <row r="62" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -6036,8 +6134,9 @@
       <c r="AU62" s="1"/>
       <c r="AV62" s="1"/>
       <c r="AW62" s="1"/>
-    </row>
-    <row r="63" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX62" s="1"/>
+    </row>
+    <row r="63" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -6087,8 +6186,9 @@
       <c r="AU63" s="1"/>
       <c r="AV63" s="1"/>
       <c r="AW63" s="1"/>
-    </row>
-    <row r="64" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX63" s="1"/>
+    </row>
+    <row r="64" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -6138,8 +6238,9 @@
       <c r="AU64" s="1"/>
       <c r="AV64" s="1"/>
       <c r="AW64" s="1"/>
-    </row>
-    <row r="65" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX64" s="1"/>
+    </row>
+    <row r="65" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -6189,8 +6290,9 @@
       <c r="AU65" s="1"/>
       <c r="AV65" s="1"/>
       <c r="AW65" s="1"/>
-    </row>
-    <row r="66" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX65" s="1"/>
+    </row>
+    <row r="66" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -6240,8 +6342,9 @@
       <c r="AU66" s="1"/>
       <c r="AV66" s="1"/>
       <c r="AW66" s="1"/>
-    </row>
-    <row r="67" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX66" s="1"/>
+    </row>
+    <row r="67" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -6291,8 +6394,9 @@
       <c r="AU67" s="1"/>
       <c r="AV67" s="1"/>
       <c r="AW67" s="1"/>
-    </row>
-    <row r="68" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX67" s="1"/>
+    </row>
+    <row r="68" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -6342,8 +6446,9 @@
       <c r="AU68" s="1"/>
       <c r="AV68" s="1"/>
       <c r="AW68" s="1"/>
-    </row>
-    <row r="69" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX68" s="1"/>
+    </row>
+    <row r="69" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -6393,8 +6498,9 @@
       <c r="AU69" s="1"/>
       <c r="AV69" s="1"/>
       <c r="AW69" s="1"/>
-    </row>
-    <row r="70" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX69" s="1"/>
+    </row>
+    <row r="70" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -6444,8 +6550,9 @@
       <c r="AU70" s="1"/>
       <c r="AV70" s="1"/>
       <c r="AW70" s="1"/>
-    </row>
-    <row r="71" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX70" s="1"/>
+    </row>
+    <row r="71" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -6495,8 +6602,9 @@
       <c r="AU71" s="1"/>
       <c r="AV71" s="1"/>
       <c r="AW71" s="1"/>
-    </row>
-    <row r="72" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX71" s="1"/>
+    </row>
+    <row r="72" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -6546,8 +6654,9 @@
       <c r="AU72" s="1"/>
       <c r="AV72" s="1"/>
       <c r="AW72" s="1"/>
-    </row>
-    <row r="73" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX72" s="1"/>
+    </row>
+    <row r="73" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -6597,8 +6706,9 @@
       <c r="AU73" s="1"/>
       <c r="AV73" s="1"/>
       <c r="AW73" s="1"/>
-    </row>
-    <row r="74" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX73" s="1"/>
+    </row>
+    <row r="74" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -6648,8 +6758,9 @@
       <c r="AU74" s="1"/>
       <c r="AV74" s="1"/>
       <c r="AW74" s="1"/>
-    </row>
-    <row r="75" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX74" s="1"/>
+    </row>
+    <row r="75" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -6699,8 +6810,9 @@
       <c r="AU75" s="1"/>
       <c r="AV75" s="1"/>
       <c r="AW75" s="1"/>
-    </row>
-    <row r="76" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX75" s="1"/>
+    </row>
+    <row r="76" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -6750,8 +6862,9 @@
       <c r="AU76" s="1"/>
       <c r="AV76" s="1"/>
       <c r="AW76" s="1"/>
-    </row>
-    <row r="77" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX76" s="1"/>
+    </row>
+    <row r="77" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -6801,8 +6914,9 @@
       <c r="AU77" s="1"/>
       <c r="AV77" s="1"/>
       <c r="AW77" s="1"/>
-    </row>
-    <row r="78" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX77" s="1"/>
+    </row>
+    <row r="78" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6852,8 +6966,9 @@
       <c r="AU78" s="1"/>
       <c r="AV78" s="1"/>
       <c r="AW78" s="1"/>
-    </row>
-    <row r="79" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX78" s="1"/>
+    </row>
+    <row r="79" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6903,8 +7018,9 @@
       <c r="AU79" s="1"/>
       <c r="AV79" s="1"/>
       <c r="AW79" s="1"/>
-    </row>
-    <row r="80" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX79" s="1"/>
+    </row>
+    <row r="80" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6954,8 +7070,9 @@
       <c r="AU80" s="1"/>
       <c r="AV80" s="1"/>
       <c r="AW80" s="1"/>
-    </row>
-    <row r="81" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX80" s="1"/>
+    </row>
+    <row r="81" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -7005,8 +7122,9 @@
       <c r="AU81" s="1"/>
       <c r="AV81" s="1"/>
       <c r="AW81" s="1"/>
-    </row>
-    <row r="82" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX81" s="1"/>
+    </row>
+    <row r="82" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7056,8 +7174,9 @@
       <c r="AU82" s="1"/>
       <c r="AV82" s="1"/>
       <c r="AW82" s="1"/>
-    </row>
-    <row r="83" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX82" s="1"/>
+    </row>
+    <row r="83" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7107,8 +7226,9 @@
       <c r="AU83" s="1"/>
       <c r="AV83" s="1"/>
       <c r="AW83" s="1"/>
-    </row>
-    <row r="84" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX83" s="1"/>
+    </row>
+    <row r="84" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7158,8 +7278,9 @@
       <c r="AU84" s="1"/>
       <c r="AV84" s="1"/>
       <c r="AW84" s="1"/>
-    </row>
-    <row r="85" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX84" s="1"/>
+    </row>
+    <row r="85" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7209,8 +7330,9 @@
       <c r="AU85" s="1"/>
       <c r="AV85" s="1"/>
       <c r="AW85" s="1"/>
-    </row>
-    <row r="86" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX85" s="1"/>
+    </row>
+    <row r="86" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7260,8 +7382,9 @@
       <c r="AU86" s="1"/>
       <c r="AV86" s="1"/>
       <c r="AW86" s="1"/>
-    </row>
-    <row r="87" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX86" s="1"/>
+    </row>
+    <row r="87" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7311,8 +7434,9 @@
       <c r="AU87" s="1"/>
       <c r="AV87" s="1"/>
       <c r="AW87" s="1"/>
-    </row>
-    <row r="88" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX87" s="1"/>
+    </row>
+    <row r="88" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7362,8 +7486,9 @@
       <c r="AU88" s="1"/>
       <c r="AV88" s="1"/>
       <c r="AW88" s="1"/>
-    </row>
-    <row r="89" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX88" s="1"/>
+    </row>
+    <row r="89" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7413,8 +7538,9 @@
       <c r="AU89" s="1"/>
       <c r="AV89" s="1"/>
       <c r="AW89" s="1"/>
-    </row>
-    <row r="90" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX89" s="1"/>
+    </row>
+    <row r="90" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7464,8 +7590,9 @@
       <c r="AU90" s="1"/>
       <c r="AV90" s="1"/>
       <c r="AW90" s="1"/>
-    </row>
-    <row r="91" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX90" s="1"/>
+    </row>
+    <row r="91" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7515,8 +7642,9 @@
       <c r="AU91" s="1"/>
       <c r="AV91" s="1"/>
       <c r="AW91" s="1"/>
-    </row>
-    <row r="92" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX91" s="1"/>
+    </row>
+    <row r="92" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7566,8 +7694,9 @@
       <c r="AU92" s="1"/>
       <c r="AV92" s="1"/>
       <c r="AW92" s="1"/>
-    </row>
-    <row r="93" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX92" s="1"/>
+    </row>
+    <row r="93" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7617,8 +7746,9 @@
       <c r="AU93" s="1"/>
       <c r="AV93" s="1"/>
       <c r="AW93" s="1"/>
-    </row>
-    <row r="94" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX93" s="1"/>
+    </row>
+    <row r="94" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7668,8 +7798,9 @@
       <c r="AU94" s="1"/>
       <c r="AV94" s="1"/>
       <c r="AW94" s="1"/>
-    </row>
-    <row r="95" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX94" s="1"/>
+    </row>
+    <row r="95" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7719,8 +7850,9 @@
       <c r="AU95" s="1"/>
       <c r="AV95" s="1"/>
       <c r="AW95" s="1"/>
-    </row>
-    <row r="96" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX95" s="1"/>
+    </row>
+    <row r="96" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7770,8 +7902,9 @@
       <c r="AU96" s="1"/>
       <c r="AV96" s="1"/>
       <c r="AW96" s="1"/>
-    </row>
-    <row r="97" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX96" s="1"/>
+    </row>
+    <row r="97" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7821,8 +7954,9 @@
       <c r="AU97" s="1"/>
       <c r="AV97" s="1"/>
       <c r="AW97" s="1"/>
-    </row>
-    <row r="98" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX97" s="1"/>
+    </row>
+    <row r="98" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7872,8 +8006,9 @@
       <c r="AU98" s="1"/>
       <c r="AV98" s="1"/>
       <c r="AW98" s="1"/>
-    </row>
-    <row r="99" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX98" s="1"/>
+    </row>
+    <row r="99" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7923,8 +8058,9 @@
       <c r="AU99" s="1"/>
       <c r="AV99" s="1"/>
       <c r="AW99" s="1"/>
-    </row>
-    <row r="100" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX99" s="1"/>
+    </row>
+    <row r="100" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7974,8 +8110,9 @@
       <c r="AU100" s="1"/>
       <c r="AV100" s="1"/>
       <c r="AW100" s="1"/>
-    </row>
-    <row r="101" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX100" s="1"/>
+    </row>
+    <row r="101" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -8025,8 +8162,9 @@
       <c r="AU101" s="1"/>
       <c r="AV101" s="1"/>
       <c r="AW101" s="1"/>
-    </row>
-    <row r="102" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX101" s="1"/>
+    </row>
+    <row r="102" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -8076,8 +8214,9 @@
       <c r="AU102" s="1"/>
       <c r="AV102" s="1"/>
       <c r="AW102" s="1"/>
-    </row>
-    <row r="103" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX102" s="1"/>
+    </row>
+    <row r="103" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -8127,8 +8266,9 @@
       <c r="AU103" s="1"/>
       <c r="AV103" s="1"/>
       <c r="AW103" s="1"/>
-    </row>
-    <row r="104" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX103" s="1"/>
+    </row>
+    <row r="104" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -8178,8 +8318,9 @@
       <c r="AU104" s="1"/>
       <c r="AV104" s="1"/>
       <c r="AW104" s="1"/>
-    </row>
-    <row r="105" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX104" s="1"/>
+    </row>
+    <row r="105" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -8229,8 +8370,9 @@
       <c r="AU105" s="1"/>
       <c r="AV105" s="1"/>
       <c r="AW105" s="1"/>
-    </row>
-    <row r="106" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX105" s="1"/>
+    </row>
+    <row r="106" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -8280,8 +8422,9 @@
       <c r="AU106" s="1"/>
       <c r="AV106" s="1"/>
       <c r="AW106" s="1"/>
-    </row>
-    <row r="107" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX106" s="1"/>
+    </row>
+    <row r="107" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -8331,8 +8474,9 @@
       <c r="AU107" s="1"/>
       <c r="AV107" s="1"/>
       <c r="AW107" s="1"/>
-    </row>
-    <row r="108" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX107" s="1"/>
+    </row>
+    <row r="108" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -8382,8 +8526,9 @@
       <c r="AU108" s="1"/>
       <c r="AV108" s="1"/>
       <c r="AW108" s="1"/>
-    </row>
-    <row r="109" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX108" s="1"/>
+    </row>
+    <row r="109" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -8433,8 +8578,9 @@
       <c r="AU109" s="1"/>
       <c r="AV109" s="1"/>
       <c r="AW109" s="1"/>
-    </row>
-    <row r="110" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX109" s="1"/>
+    </row>
+    <row r="110" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -8484,8 +8630,9 @@
       <c r="AU110" s="1"/>
       <c r="AV110" s="1"/>
       <c r="AW110" s="1"/>
-    </row>
-    <row r="111" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX110" s="1"/>
+    </row>
+    <row r="111" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -8535,8 +8682,9 @@
       <c r="AU111" s="1"/>
       <c r="AV111" s="1"/>
       <c r="AW111" s="1"/>
-    </row>
-    <row r="112" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX111" s="1"/>
+    </row>
+    <row r="112" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -8586,8 +8734,9 @@
       <c r="AU112" s="1"/>
       <c r="AV112" s="1"/>
       <c r="AW112" s="1"/>
-    </row>
-    <row r="113" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX112" s="1"/>
+    </row>
+    <row r="113" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -8637,8 +8786,9 @@
       <c r="AU113" s="1"/>
       <c r="AV113" s="1"/>
       <c r="AW113" s="1"/>
-    </row>
-    <row r="114" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX113" s="1"/>
+    </row>
+    <row r="114" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -8688,8 +8838,9 @@
       <c r="AU114" s="1"/>
       <c r="AV114" s="1"/>
       <c r="AW114" s="1"/>
-    </row>
-    <row r="115" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX114" s="1"/>
+    </row>
+    <row r="115" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -8739,8 +8890,9 @@
       <c r="AU115" s="1"/>
       <c r="AV115" s="1"/>
       <c r="AW115" s="1"/>
-    </row>
-    <row r="116" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX115" s="1"/>
+    </row>
+    <row r="116" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -8790,8 +8942,9 @@
       <c r="AU116" s="1"/>
       <c r="AV116" s="1"/>
       <c r="AW116" s="1"/>
-    </row>
-    <row r="117" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX116" s="1"/>
+    </row>
+    <row r="117" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -8841,8 +8994,9 @@
       <c r="AU117" s="1"/>
       <c r="AV117" s="1"/>
       <c r="AW117" s="1"/>
-    </row>
-    <row r="118" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX117" s="1"/>
+    </row>
+    <row r="118" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -8892,8 +9046,9 @@
       <c r="AU118" s="1"/>
       <c r="AV118" s="1"/>
       <c r="AW118" s="1"/>
-    </row>
-    <row r="119" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX118" s="1"/>
+    </row>
+    <row r="119" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -8943,8 +9098,9 @@
       <c r="AU119" s="1"/>
       <c r="AV119" s="1"/>
       <c r="AW119" s="1"/>
-    </row>
-    <row r="120" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX119" s="1"/>
+    </row>
+    <row r="120" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -8994,8 +9150,9 @@
       <c r="AU120" s="1"/>
       <c r="AV120" s="1"/>
       <c r="AW120" s="1"/>
-    </row>
-    <row r="121" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX120" s="1"/>
+    </row>
+    <row r="121" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -9045,8 +9202,9 @@
       <c r="AU121" s="1"/>
       <c r="AV121" s="1"/>
       <c r="AW121" s="1"/>
-    </row>
-    <row r="122" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX121" s="1"/>
+    </row>
+    <row r="122" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -9096,8 +9254,9 @@
       <c r="AU122" s="1"/>
       <c r="AV122" s="1"/>
       <c r="AW122" s="1"/>
-    </row>
-    <row r="123" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX122" s="1"/>
+    </row>
+    <row r="123" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -9147,8 +9306,9 @@
       <c r="AU123" s="1"/>
       <c r="AV123" s="1"/>
       <c r="AW123" s="1"/>
-    </row>
-    <row r="124" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX123" s="1"/>
+    </row>
+    <row r="124" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -9198,8 +9358,9 @@
       <c r="AU124" s="1"/>
       <c r="AV124" s="1"/>
       <c r="AW124" s="1"/>
-    </row>
-    <row r="125" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX124" s="1"/>
+    </row>
+    <row r="125" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -9249,8 +9410,9 @@
       <c r="AU125" s="1"/>
       <c r="AV125" s="1"/>
       <c r="AW125" s="1"/>
-    </row>
-    <row r="126" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX125" s="1"/>
+    </row>
+    <row r="126" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -9300,8 +9462,9 @@
       <c r="AU126" s="1"/>
       <c r="AV126" s="1"/>
       <c r="AW126" s="1"/>
-    </row>
-    <row r="127" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX126" s="1"/>
+    </row>
+    <row r="127" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -9351,8 +9514,9 @@
       <c r="AU127" s="1"/>
       <c r="AV127" s="1"/>
       <c r="AW127" s="1"/>
-    </row>
-    <row r="128" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX127" s="1"/>
+    </row>
+    <row r="128" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -9402,8 +9566,9 @@
       <c r="AU128" s="1"/>
       <c r="AV128" s="1"/>
       <c r="AW128" s="1"/>
-    </row>
-    <row r="129" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX128" s="1"/>
+    </row>
+    <row r="129" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -9453,8 +9618,9 @@
       <c r="AU129" s="1"/>
       <c r="AV129" s="1"/>
       <c r="AW129" s="1"/>
-    </row>
-    <row r="130" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX129" s="1"/>
+    </row>
+    <row r="130" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -9504,8 +9670,9 @@
       <c r="AU130" s="1"/>
       <c r="AV130" s="1"/>
       <c r="AW130" s="1"/>
-    </row>
-    <row r="131" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX130" s="1"/>
+    </row>
+    <row r="131" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -9555,8 +9722,9 @@
       <c r="AU131" s="1"/>
       <c r="AV131" s="1"/>
       <c r="AW131" s="1"/>
-    </row>
-    <row r="132" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX131" s="1"/>
+    </row>
+    <row r="132" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -9606,8 +9774,9 @@
       <c r="AU132" s="1"/>
       <c r="AV132" s="1"/>
       <c r="AW132" s="1"/>
-    </row>
-    <row r="133" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX132" s="1"/>
+    </row>
+    <row r="133" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -9657,8 +9826,9 @@
       <c r="AU133" s="1"/>
       <c r="AV133" s="1"/>
       <c r="AW133" s="1"/>
-    </row>
-    <row r="134" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX133" s="1"/>
+    </row>
+    <row r="134" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -9708,8 +9878,9 @@
       <c r="AU134" s="1"/>
       <c r="AV134" s="1"/>
       <c r="AW134" s="1"/>
-    </row>
-    <row r="135" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX134" s="1"/>
+    </row>
+    <row r="135" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -9759,8 +9930,9 @@
       <c r="AU135" s="1"/>
       <c r="AV135" s="1"/>
       <c r="AW135" s="1"/>
-    </row>
-    <row r="136" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX135" s="1"/>
+    </row>
+    <row r="136" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -9810,8 +9982,9 @@
       <c r="AU136" s="1"/>
       <c r="AV136" s="1"/>
       <c r="AW136" s="1"/>
-    </row>
-    <row r="137" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX136" s="1"/>
+    </row>
+    <row r="137" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -9861,8 +10034,9 @@
       <c r="AU137" s="1"/>
       <c r="AV137" s="1"/>
       <c r="AW137" s="1"/>
-    </row>
-    <row r="138" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX137" s="1"/>
+    </row>
+    <row r="138" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -9912,8 +10086,9 @@
       <c r="AU138" s="1"/>
       <c r="AV138" s="1"/>
       <c r="AW138" s="1"/>
-    </row>
-    <row r="139" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX138" s="1"/>
+    </row>
+    <row r="139" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -9963,8 +10138,9 @@
       <c r="AU139" s="1"/>
       <c r="AV139" s="1"/>
       <c r="AW139" s="1"/>
-    </row>
-    <row r="140" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX139" s="1"/>
+    </row>
+    <row r="140" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -10014,8 +10190,9 @@
       <c r="AU140" s="1"/>
       <c r="AV140" s="1"/>
       <c r="AW140" s="1"/>
-    </row>
-    <row r="141" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX140" s="1"/>
+    </row>
+    <row r="141" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -10065,8 +10242,9 @@
       <c r="AU141" s="1"/>
       <c r="AV141" s="1"/>
       <c r="AW141" s="1"/>
-    </row>
-    <row r="142" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX141" s="1"/>
+    </row>
+    <row r="142" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -10116,8 +10294,9 @@
       <c r="AU142" s="1"/>
       <c r="AV142" s="1"/>
       <c r="AW142" s="1"/>
-    </row>
-    <row r="143" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX142" s="1"/>
+    </row>
+    <row r="143" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -10167,8 +10346,9 @@
       <c r="AU143" s="1"/>
       <c r="AV143" s="1"/>
       <c r="AW143" s="1"/>
-    </row>
-    <row r="144" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX143" s="1"/>
+    </row>
+    <row r="144" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -10218,8 +10398,9 @@
       <c r="AU144" s="1"/>
       <c r="AV144" s="1"/>
       <c r="AW144" s="1"/>
-    </row>
-    <row r="145" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX144" s="1"/>
+    </row>
+    <row r="145" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -10269,8 +10450,9 @@
       <c r="AU145" s="1"/>
       <c r="AV145" s="1"/>
       <c r="AW145" s="1"/>
-    </row>
-    <row r="146" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX145" s="1"/>
+    </row>
+    <row r="146" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -10320,8 +10502,9 @@
       <c r="AU146" s="1"/>
       <c r="AV146" s="1"/>
       <c r="AW146" s="1"/>
-    </row>
-    <row r="147" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX146" s="1"/>
+    </row>
+    <row r="147" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -10371,8 +10554,9 @@
       <c r="AU147" s="1"/>
       <c r="AV147" s="1"/>
       <c r="AW147" s="1"/>
-    </row>
-    <row r="148" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX147" s="1"/>
+    </row>
+    <row r="148" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -10422,8 +10606,9 @@
       <c r="AU148" s="1"/>
       <c r="AV148" s="1"/>
       <c r="AW148" s="1"/>
-    </row>
-    <row r="149" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX148" s="1"/>
+    </row>
+    <row r="149" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -10473,8 +10658,9 @@
       <c r="AU149" s="1"/>
       <c r="AV149" s="1"/>
       <c r="AW149" s="1"/>
-    </row>
-    <row r="150" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX149" s="1"/>
+    </row>
+    <row r="150" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -10524,8 +10710,9 @@
       <c r="AU150" s="1"/>
       <c r="AV150" s="1"/>
       <c r="AW150" s="1"/>
-    </row>
-    <row r="151" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX150" s="1"/>
+    </row>
+    <row r="151" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -10575,8 +10762,9 @@
       <c r="AU151" s="1"/>
       <c r="AV151" s="1"/>
       <c r="AW151" s="1"/>
-    </row>
-    <row r="152" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX151" s="1"/>
+    </row>
+    <row r="152" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -10626,8 +10814,9 @@
       <c r="AU152" s="1"/>
       <c r="AV152" s="1"/>
       <c r="AW152" s="1"/>
-    </row>
-    <row r="153" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX152" s="1"/>
+    </row>
+    <row r="153" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -10677,8 +10866,9 @@
       <c r="AU153" s="1"/>
       <c r="AV153" s="1"/>
       <c r="AW153" s="1"/>
-    </row>
-    <row r="154" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX153" s="1"/>
+    </row>
+    <row r="154" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -10728,8 +10918,9 @@
       <c r="AU154" s="1"/>
       <c r="AV154" s="1"/>
       <c r="AW154" s="1"/>
-    </row>
-    <row r="155" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX154" s="1"/>
+    </row>
+    <row r="155" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -10779,8 +10970,9 @@
       <c r="AU155" s="1"/>
       <c r="AV155" s="1"/>
       <c r="AW155" s="1"/>
-    </row>
-    <row r="156" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX155" s="1"/>
+    </row>
+    <row r="156" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -10830,8 +11022,9 @@
       <c r="AU156" s="1"/>
       <c r="AV156" s="1"/>
       <c r="AW156" s="1"/>
-    </row>
-    <row r="157" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX156" s="1"/>
+    </row>
+    <row r="157" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -10881,8 +11074,9 @@
       <c r="AU157" s="1"/>
       <c r="AV157" s="1"/>
       <c r="AW157" s="1"/>
-    </row>
-    <row r="158" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX157" s="1"/>
+    </row>
+    <row r="158" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -10932,8 +11126,9 @@
       <c r="AU158" s="1"/>
       <c r="AV158" s="1"/>
       <c r="AW158" s="1"/>
-    </row>
-    <row r="159" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX158" s="1"/>
+    </row>
+    <row r="159" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -10983,8 +11178,9 @@
       <c r="AU159" s="1"/>
       <c r="AV159" s="1"/>
       <c r="AW159" s="1"/>
-    </row>
-    <row r="160" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX159" s="1"/>
+    </row>
+    <row r="160" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -11034,8 +11230,9 @@
       <c r="AU160" s="1"/>
       <c r="AV160" s="1"/>
       <c r="AW160" s="1"/>
-    </row>
-    <row r="161" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX160" s="1"/>
+    </row>
+    <row r="161" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -11085,8 +11282,9 @@
       <c r="AU161" s="1"/>
       <c r="AV161" s="1"/>
       <c r="AW161" s="1"/>
-    </row>
-    <row r="162" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX161" s="1"/>
+    </row>
+    <row r="162" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -11136,8 +11334,9 @@
       <c r="AU162" s="1"/>
       <c r="AV162" s="1"/>
       <c r="AW162" s="1"/>
-    </row>
-    <row r="163" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX162" s="1"/>
+    </row>
+    <row r="163" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -11187,8 +11386,9 @@
       <c r="AU163" s="1"/>
       <c r="AV163" s="1"/>
       <c r="AW163" s="1"/>
-    </row>
-    <row r="164" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX163" s="1"/>
+    </row>
+    <row r="164" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -11238,8 +11438,9 @@
       <c r="AU164" s="1"/>
       <c r="AV164" s="1"/>
       <c r="AW164" s="1"/>
-    </row>
-    <row r="165" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX164" s="1"/>
+    </row>
+    <row r="165" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -11289,8 +11490,9 @@
       <c r="AU165" s="1"/>
       <c r="AV165" s="1"/>
       <c r="AW165" s="1"/>
-    </row>
-    <row r="166" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX165" s="1"/>
+    </row>
+    <row r="166" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -11340,8 +11542,9 @@
       <c r="AU166" s="1"/>
       <c r="AV166" s="1"/>
       <c r="AW166" s="1"/>
-    </row>
-    <row r="167" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX166" s="1"/>
+    </row>
+    <row r="167" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -11391,8 +11594,9 @@
       <c r="AU167" s="1"/>
       <c r="AV167" s="1"/>
       <c r="AW167" s="1"/>
-    </row>
-    <row r="168" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX167" s="1"/>
+    </row>
+    <row r="168" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -11442,8 +11646,9 @@
       <c r="AU168" s="1"/>
       <c r="AV168" s="1"/>
       <c r="AW168" s="1"/>
-    </row>
-    <row r="169" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX168" s="1"/>
+    </row>
+    <row r="169" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -11493,8 +11698,9 @@
       <c r="AU169" s="1"/>
       <c r="AV169" s="1"/>
       <c r="AW169" s="1"/>
-    </row>
-    <row r="170" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX169" s="1"/>
+    </row>
+    <row r="170" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -11544,8 +11750,9 @@
       <c r="AU170" s="1"/>
       <c r="AV170" s="1"/>
       <c r="AW170" s="1"/>
-    </row>
-    <row r="171" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX170" s="1"/>
+    </row>
+    <row r="171" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -11595,8 +11802,9 @@
       <c r="AU171" s="1"/>
       <c r="AV171" s="1"/>
       <c r="AW171" s="1"/>
-    </row>
-    <row r="172" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX171" s="1"/>
+    </row>
+    <row r="172" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -11646,8 +11854,9 @@
       <c r="AU172" s="1"/>
       <c r="AV172" s="1"/>
       <c r="AW172" s="1"/>
-    </row>
-    <row r="173" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX172" s="1"/>
+    </row>
+    <row r="173" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -11697,8 +11906,9 @@
       <c r="AU173" s="1"/>
       <c r="AV173" s="1"/>
       <c r="AW173" s="1"/>
-    </row>
-    <row r="174" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX173" s="1"/>
+    </row>
+    <row r="174" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -11748,8 +11958,9 @@
       <c r="AU174" s="1"/>
       <c r="AV174" s="1"/>
       <c r="AW174" s="1"/>
-    </row>
-    <row r="175" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX174" s="1"/>
+    </row>
+    <row r="175" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -11799,8 +12010,9 @@
       <c r="AU175" s="1"/>
       <c r="AV175" s="1"/>
       <c r="AW175" s="1"/>
-    </row>
-    <row r="176" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX175" s="1"/>
+    </row>
+    <row r="176" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -11850,8 +12062,9 @@
       <c r="AU176" s="1"/>
       <c r="AV176" s="1"/>
       <c r="AW176" s="1"/>
-    </row>
-    <row r="177" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX176" s="1"/>
+    </row>
+    <row r="177" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -11901,8 +12114,9 @@
       <c r="AU177" s="1"/>
       <c r="AV177" s="1"/>
       <c r="AW177" s="1"/>
-    </row>
-    <row r="178" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX177" s="1"/>
+    </row>
+    <row r="178" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -11952,8 +12166,9 @@
       <c r="AU178" s="1"/>
       <c r="AV178" s="1"/>
       <c r="AW178" s="1"/>
-    </row>
-    <row r="179" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX178" s="1"/>
+    </row>
+    <row r="179" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -12003,8 +12218,9 @@
       <c r="AU179" s="1"/>
       <c r="AV179" s="1"/>
       <c r="AW179" s="1"/>
-    </row>
-    <row r="180" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX179" s="1"/>
+    </row>
+    <row r="180" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -12054,8 +12270,9 @@
       <c r="AU180" s="1"/>
       <c r="AV180" s="1"/>
       <c r="AW180" s="1"/>
-    </row>
-    <row r="181" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX180" s="1"/>
+    </row>
+    <row r="181" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -12105,8 +12322,9 @@
       <c r="AU181" s="1"/>
       <c r="AV181" s="1"/>
       <c r="AW181" s="1"/>
-    </row>
-    <row r="182" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX181" s="1"/>
+    </row>
+    <row r="182" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -12156,8 +12374,9 @@
       <c r="AU182" s="1"/>
       <c r="AV182" s="1"/>
       <c r="AW182" s="1"/>
-    </row>
-    <row r="183" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX182" s="1"/>
+    </row>
+    <row r="183" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -12207,8 +12426,9 @@
       <c r="AU183" s="1"/>
       <c r="AV183" s="1"/>
       <c r="AW183" s="1"/>
-    </row>
-    <row r="184" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX183" s="1"/>
+    </row>
+    <row r="184" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -12258,8 +12478,9 @@
       <c r="AU184" s="1"/>
       <c r="AV184" s="1"/>
       <c r="AW184" s="1"/>
-    </row>
-    <row r="185" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX184" s="1"/>
+    </row>
+    <row r="185" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -12309,8 +12530,9 @@
       <c r="AU185" s="1"/>
       <c r="AV185" s="1"/>
       <c r="AW185" s="1"/>
-    </row>
-    <row r="186" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX185" s="1"/>
+    </row>
+    <row r="186" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -12360,8 +12582,9 @@
       <c r="AU186" s="1"/>
       <c r="AV186" s="1"/>
       <c r="AW186" s="1"/>
-    </row>
-    <row r="187" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX186" s="1"/>
+    </row>
+    <row r="187" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -12411,8 +12634,9 @@
       <c r="AU187" s="1"/>
       <c r="AV187" s="1"/>
       <c r="AW187" s="1"/>
-    </row>
-    <row r="188" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX187" s="1"/>
+    </row>
+    <row r="188" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -12462,8 +12686,9 @@
       <c r="AU188" s="1"/>
       <c r="AV188" s="1"/>
       <c r="AW188" s="1"/>
-    </row>
-    <row r="189" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX188" s="1"/>
+    </row>
+    <row r="189" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -12513,8 +12738,9 @@
       <c r="AU189" s="1"/>
       <c r="AV189" s="1"/>
       <c r="AW189" s="1"/>
-    </row>
-    <row r="190" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX189" s="1"/>
+    </row>
+    <row r="190" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -12564,8 +12790,9 @@
       <c r="AU190" s="1"/>
       <c r="AV190" s="1"/>
       <c r="AW190" s="1"/>
-    </row>
-    <row r="191" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX190" s="1"/>
+    </row>
+    <row r="191" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -12615,8 +12842,9 @@
       <c r="AU191" s="1"/>
       <c r="AV191" s="1"/>
       <c r="AW191" s="1"/>
-    </row>
-    <row r="192" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX191" s="1"/>
+    </row>
+    <row r="192" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -12666,8 +12894,9 @@
       <c r="AU192" s="1"/>
       <c r="AV192" s="1"/>
       <c r="AW192" s="1"/>
-    </row>
-    <row r="193" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX192" s="1"/>
+    </row>
+    <row r="193" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -12717,8 +12946,9 @@
       <c r="AU193" s="1"/>
       <c r="AV193" s="1"/>
       <c r="AW193" s="1"/>
-    </row>
-    <row r="194" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX193" s="1"/>
+    </row>
+    <row r="194" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -12768,8 +12998,9 @@
       <c r="AU194" s="1"/>
       <c r="AV194" s="1"/>
       <c r="AW194" s="1"/>
-    </row>
-    <row r="195" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX194" s="1"/>
+    </row>
+    <row r="195" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -12819,8 +13050,9 @@
       <c r="AU195" s="1"/>
       <c r="AV195" s="1"/>
       <c r="AW195" s="1"/>
-    </row>
-    <row r="196" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX195" s="1"/>
+    </row>
+    <row r="196" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -12870,8 +13102,9 @@
       <c r="AU196" s="1"/>
       <c r="AV196" s="1"/>
       <c r="AW196" s="1"/>
-    </row>
-    <row r="197" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX196" s="1"/>
+    </row>
+    <row r="197" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -12921,8 +13154,9 @@
       <c r="AU197" s="1"/>
       <c r="AV197" s="1"/>
       <c r="AW197" s="1"/>
-    </row>
-    <row r="198" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX197" s="1"/>
+    </row>
+    <row r="198" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -12972,8 +13206,9 @@
       <c r="AU198" s="1"/>
       <c r="AV198" s="1"/>
       <c r="AW198" s="1"/>
-    </row>
-    <row r="199" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX198" s="1"/>
+    </row>
+    <row r="199" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -13023,8 +13258,9 @@
       <c r="AU199" s="1"/>
       <c r="AV199" s="1"/>
       <c r="AW199" s="1"/>
-    </row>
-    <row r="200" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX199" s="1"/>
+    </row>
+    <row r="200" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -13074,8 +13310,9 @@
       <c r="AU200" s="1"/>
       <c r="AV200" s="1"/>
       <c r="AW200" s="1"/>
-    </row>
-    <row r="201" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX200" s="1"/>
+    </row>
+    <row r="201" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -13125,8 +13362,9 @@
       <c r="AU201" s="1"/>
       <c r="AV201" s="1"/>
       <c r="AW201" s="1"/>
-    </row>
-    <row r="202" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX201" s="1"/>
+    </row>
+    <row r="202" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -13176,8 +13414,9 @@
       <c r="AU202" s="1"/>
       <c r="AV202" s="1"/>
       <c r="AW202" s="1"/>
-    </row>
-    <row r="203" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX202" s="1"/>
+    </row>
+    <row r="203" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -13227,8 +13466,9 @@
       <c r="AU203" s="1"/>
       <c r="AV203" s="1"/>
       <c r="AW203" s="1"/>
-    </row>
-    <row r="204" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX203" s="1"/>
+    </row>
+    <row r="204" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -13278,8 +13518,9 @@
       <c r="AU204" s="1"/>
       <c r="AV204" s="1"/>
       <c r="AW204" s="1"/>
-    </row>
-    <row r="205" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX204" s="1"/>
+    </row>
+    <row r="205" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -13329,8 +13570,9 @@
       <c r="AU205" s="1"/>
       <c r="AV205" s="1"/>
       <c r="AW205" s="1"/>
-    </row>
-    <row r="206" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX205" s="1"/>
+    </row>
+    <row r="206" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -13380,8 +13622,9 @@
       <c r="AU206" s="1"/>
       <c r="AV206" s="1"/>
       <c r="AW206" s="1"/>
-    </row>
-    <row r="207" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX206" s="1"/>
+    </row>
+    <row r="207" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -13431,8 +13674,9 @@
       <c r="AU207" s="1"/>
       <c r="AV207" s="1"/>
       <c r="AW207" s="1"/>
-    </row>
-    <row r="208" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX207" s="1"/>
+    </row>
+    <row r="208" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -13482,8 +13726,9 @@
       <c r="AU208" s="1"/>
       <c r="AV208" s="1"/>
       <c r="AW208" s="1"/>
-    </row>
-    <row r="209" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX208" s="1"/>
+    </row>
+    <row r="209" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -13533,8 +13778,9 @@
       <c r="AU209" s="1"/>
       <c r="AV209" s="1"/>
       <c r="AW209" s="1"/>
-    </row>
-    <row r="210" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX209" s="1"/>
+    </row>
+    <row r="210" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -13584,8 +13830,9 @@
       <c r="AU210" s="1"/>
       <c r="AV210" s="1"/>
       <c r="AW210" s="1"/>
-    </row>
-    <row r="211" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX210" s="1"/>
+    </row>
+    <row r="211" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -13635,8 +13882,9 @@
       <c r="AU211" s="1"/>
       <c r="AV211" s="1"/>
       <c r="AW211" s="1"/>
-    </row>
-    <row r="212" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX211" s="1"/>
+    </row>
+    <row r="212" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -13686,8 +13934,9 @@
       <c r="AU212" s="1"/>
       <c r="AV212" s="1"/>
       <c r="AW212" s="1"/>
-    </row>
-    <row r="213" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX212" s="1"/>
+    </row>
+    <row r="213" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -13737,8 +13986,9 @@
       <c r="AU213" s="1"/>
       <c r="AV213" s="1"/>
       <c r="AW213" s="1"/>
-    </row>
-    <row r="214" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX213" s="1"/>
+    </row>
+    <row r="214" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -13788,8 +14038,9 @@
       <c r="AU214" s="1"/>
       <c r="AV214" s="1"/>
       <c r="AW214" s="1"/>
-    </row>
-    <row r="215" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX214" s="1"/>
+    </row>
+    <row r="215" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -13839,8 +14090,9 @@
       <c r="AU215" s="1"/>
       <c r="AV215" s="1"/>
       <c r="AW215" s="1"/>
-    </row>
-    <row r="216" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX215" s="1"/>
+    </row>
+    <row r="216" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -13890,8 +14142,9 @@
       <c r="AU216" s="1"/>
       <c r="AV216" s="1"/>
       <c r="AW216" s="1"/>
-    </row>
-    <row r="217" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX216" s="1"/>
+    </row>
+    <row r="217" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -13941,8 +14194,9 @@
       <c r="AU217" s="1"/>
       <c r="AV217" s="1"/>
       <c r="AW217" s="1"/>
-    </row>
-    <row r="218" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX217" s="1"/>
+    </row>
+    <row r="218" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -13992,8 +14246,9 @@
       <c r="AU218" s="1"/>
       <c r="AV218" s="1"/>
       <c r="AW218" s="1"/>
-    </row>
-    <row r="219" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX218" s="1"/>
+    </row>
+    <row r="219" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -14043,8 +14298,9 @@
       <c r="AU219" s="1"/>
       <c r="AV219" s="1"/>
       <c r="AW219" s="1"/>
-    </row>
-    <row r="220" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX219" s="1"/>
+    </row>
+    <row r="220" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -14094,8 +14350,9 @@
       <c r="AU220" s="1"/>
       <c r="AV220" s="1"/>
       <c r="AW220" s="1"/>
-    </row>
-    <row r="221" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX220" s="1"/>
+    </row>
+    <row r="221" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -14145,8 +14402,9 @@
       <c r="AU221" s="1"/>
       <c r="AV221" s="1"/>
       <c r="AW221" s="1"/>
-    </row>
-    <row r="222" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX221" s="1"/>
+    </row>
+    <row r="222" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -14196,8 +14454,9 @@
       <c r="AU222" s="1"/>
       <c r="AV222" s="1"/>
       <c r="AW222" s="1"/>
-    </row>
-    <row r="223" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX222" s="1"/>
+    </row>
+    <row r="223" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -14247,8 +14506,9 @@
       <c r="AU223" s="1"/>
       <c r="AV223" s="1"/>
       <c r="AW223" s="1"/>
-    </row>
-    <row r="224" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX223" s="1"/>
+    </row>
+    <row r="224" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -14298,8 +14558,9 @@
       <c r="AU224" s="1"/>
       <c r="AV224" s="1"/>
       <c r="AW224" s="1"/>
-    </row>
-    <row r="225" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX224" s="1"/>
+    </row>
+    <row r="225" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -14349,8 +14610,9 @@
       <c r="AU225" s="1"/>
       <c r="AV225" s="1"/>
       <c r="AW225" s="1"/>
-    </row>
-    <row r="226" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX225" s="1"/>
+    </row>
+    <row r="226" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -14400,8 +14662,9 @@
       <c r="AU226" s="1"/>
       <c r="AV226" s="1"/>
       <c r="AW226" s="1"/>
-    </row>
-    <row r="227" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX226" s="1"/>
+    </row>
+    <row r="227" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -14451,8 +14714,9 @@
       <c r="AU227" s="1"/>
       <c r="AV227" s="1"/>
       <c r="AW227" s="1"/>
-    </row>
-    <row r="228" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX227" s="1"/>
+    </row>
+    <row r="228" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -14502,8 +14766,9 @@
       <c r="AU228" s="1"/>
       <c r="AV228" s="1"/>
       <c r="AW228" s="1"/>
-    </row>
-    <row r="229" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX228" s="1"/>
+    </row>
+    <row r="229" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -14553,8 +14818,9 @@
       <c r="AU229" s="1"/>
       <c r="AV229" s="1"/>
       <c r="AW229" s="1"/>
-    </row>
-    <row r="230" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX229" s="1"/>
+    </row>
+    <row r="230" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -14604,8 +14870,9 @@
       <c r="AU230" s="1"/>
       <c r="AV230" s="1"/>
       <c r="AW230" s="1"/>
-    </row>
-    <row r="231" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX230" s="1"/>
+    </row>
+    <row r="231" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -14655,8 +14922,9 @@
       <c r="AU231" s="1"/>
       <c r="AV231" s="1"/>
       <c r="AW231" s="1"/>
-    </row>
-    <row r="232" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX231" s="1"/>
+    </row>
+    <row r="232" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -14706,8 +14974,9 @@
       <c r="AU232" s="1"/>
       <c r="AV232" s="1"/>
       <c r="AW232" s="1"/>
-    </row>
-    <row r="233" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX232" s="1"/>
+    </row>
+    <row r="233" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -14757,8 +15026,9 @@
       <c r="AU233" s="1"/>
       <c r="AV233" s="1"/>
       <c r="AW233" s="1"/>
-    </row>
-    <row r="234" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX233" s="1"/>
+    </row>
+    <row r="234" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -14808,8 +15078,9 @@
       <c r="AU234" s="1"/>
       <c r="AV234" s="1"/>
       <c r="AW234" s="1"/>
-    </row>
-    <row r="235" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX234" s="1"/>
+    </row>
+    <row r="235" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -14859,8 +15130,9 @@
       <c r="AU235" s="1"/>
       <c r="AV235" s="1"/>
       <c r="AW235" s="1"/>
-    </row>
-    <row r="236" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX235" s="1"/>
+    </row>
+    <row r="236" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -14910,8 +15182,9 @@
       <c r="AU236" s="1"/>
       <c r="AV236" s="1"/>
       <c r="AW236" s="1"/>
-    </row>
-    <row r="237" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX236" s="1"/>
+    </row>
+    <row r="237" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -14961,8 +15234,9 @@
       <c r="AU237" s="1"/>
       <c r="AV237" s="1"/>
       <c r="AW237" s="1"/>
-    </row>
-    <row r="238" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX237" s="1"/>
+    </row>
+    <row r="238" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -15012,8 +15286,9 @@
       <c r="AU238" s="1"/>
       <c r="AV238" s="1"/>
       <c r="AW238" s="1"/>
-    </row>
-    <row r="239" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX238" s="1"/>
+    </row>
+    <row r="239" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -15063,8 +15338,9 @@
       <c r="AU239" s="1"/>
       <c r="AV239" s="1"/>
       <c r="AW239" s="1"/>
-    </row>
-    <row r="240" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX239" s="1"/>
+    </row>
+    <row r="240" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -15114,8 +15390,9 @@
       <c r="AU240" s="1"/>
       <c r="AV240" s="1"/>
       <c r="AW240" s="1"/>
-    </row>
-    <row r="241" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX240" s="1"/>
+    </row>
+    <row r="241" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -15165,8 +15442,9 @@
       <c r="AU241" s="1"/>
       <c r="AV241" s="1"/>
       <c r="AW241" s="1"/>
-    </row>
-    <row r="242" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX241" s="1"/>
+    </row>
+    <row r="242" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -15216,8 +15494,9 @@
       <c r="AU242" s="1"/>
       <c r="AV242" s="1"/>
       <c r="AW242" s="1"/>
-    </row>
-    <row r="243" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX242" s="1"/>
+    </row>
+    <row r="243" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -15267,8 +15546,9 @@
       <c r="AU243" s="1"/>
       <c r="AV243" s="1"/>
       <c r="AW243" s="1"/>
-    </row>
-    <row r="244" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX243" s="1"/>
+    </row>
+    <row r="244" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -15318,8 +15598,9 @@
       <c r="AU244" s="1"/>
       <c r="AV244" s="1"/>
       <c r="AW244" s="1"/>
-    </row>
-    <row r="245" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX244" s="1"/>
+    </row>
+    <row r="245" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -15369,8 +15650,9 @@
       <c r="AU245" s="1"/>
       <c r="AV245" s="1"/>
       <c r="AW245" s="1"/>
-    </row>
-    <row r="246" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX245" s="1"/>
+    </row>
+    <row r="246" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -15420,8 +15702,9 @@
       <c r="AU246" s="1"/>
       <c r="AV246" s="1"/>
       <c r="AW246" s="1"/>
-    </row>
-    <row r="247" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX246" s="1"/>
+    </row>
+    <row r="247" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -15471,8 +15754,9 @@
       <c r="AU247" s="1"/>
       <c r="AV247" s="1"/>
       <c r="AW247" s="1"/>
-    </row>
-    <row r="248" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX247" s="1"/>
+    </row>
+    <row r="248" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -15522,8 +15806,9 @@
       <c r="AU248" s="1"/>
       <c r="AV248" s="1"/>
       <c r="AW248" s="1"/>
-    </row>
-    <row r="249" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX248" s="1"/>
+    </row>
+    <row r="249" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -15573,8 +15858,9 @@
       <c r="AU249" s="1"/>
       <c r="AV249" s="1"/>
       <c r="AW249" s="1"/>
-    </row>
-    <row r="250" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX249" s="1"/>
+    </row>
+    <row r="250" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -15624,8 +15910,9 @@
       <c r="AU250" s="1"/>
       <c r="AV250" s="1"/>
       <c r="AW250" s="1"/>
-    </row>
-    <row r="251" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX250" s="1"/>
+    </row>
+    <row r="251" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -15675,8 +15962,9 @@
       <c r="AU251" s="1"/>
       <c r="AV251" s="1"/>
       <c r="AW251" s="1"/>
-    </row>
-    <row r="252" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX251" s="1"/>
+    </row>
+    <row r="252" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -15726,8 +16014,9 @@
       <c r="AU252" s="1"/>
       <c r="AV252" s="1"/>
       <c r="AW252" s="1"/>
-    </row>
-    <row r="253" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX252" s="1"/>
+    </row>
+    <row r="253" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -15777,8 +16066,9 @@
       <c r="AU253" s="1"/>
       <c r="AV253" s="1"/>
       <c r="AW253" s="1"/>
-    </row>
-    <row r="254" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX253" s="1"/>
+    </row>
+    <row r="254" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -15828,8 +16118,9 @@
       <c r="AU254" s="1"/>
       <c r="AV254" s="1"/>
       <c r="AW254" s="1"/>
-    </row>
-    <row r="255" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX254" s="1"/>
+    </row>
+    <row r="255" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -15879,8 +16170,9 @@
       <c r="AU255" s="1"/>
       <c r="AV255" s="1"/>
       <c r="AW255" s="1"/>
-    </row>
-    <row r="256" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX255" s="1"/>
+    </row>
+    <row r="256" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -15930,8 +16222,9 @@
       <c r="AU256" s="1"/>
       <c r="AV256" s="1"/>
       <c r="AW256" s="1"/>
-    </row>
-    <row r="257" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX256" s="1"/>
+    </row>
+    <row r="257" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -15981,8 +16274,9 @@
       <c r="AU257" s="1"/>
       <c r="AV257" s="1"/>
       <c r="AW257" s="1"/>
-    </row>
-    <row r="258" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX257" s="1"/>
+    </row>
+    <row r="258" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -16032,8 +16326,9 @@
       <c r="AU258" s="1"/>
       <c r="AV258" s="1"/>
       <c r="AW258" s="1"/>
-    </row>
-    <row r="259" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX258" s="1"/>
+    </row>
+    <row r="259" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -16083,8 +16378,9 @@
       <c r="AU259" s="1"/>
       <c r="AV259" s="1"/>
       <c r="AW259" s="1"/>
-    </row>
-    <row r="260" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX259" s="1"/>
+    </row>
+    <row r="260" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -16134,8 +16430,9 @@
       <c r="AU260" s="1"/>
       <c r="AV260" s="1"/>
       <c r="AW260" s="1"/>
-    </row>
-    <row r="261" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX260" s="1"/>
+    </row>
+    <row r="261" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -16185,8 +16482,9 @@
       <c r="AU261" s="1"/>
       <c r="AV261" s="1"/>
       <c r="AW261" s="1"/>
-    </row>
-    <row r="262" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX261" s="1"/>
+    </row>
+    <row r="262" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -16236,8 +16534,9 @@
       <c r="AU262" s="1"/>
       <c r="AV262" s="1"/>
       <c r="AW262" s="1"/>
-    </row>
-    <row r="263" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX262" s="1"/>
+    </row>
+    <row r="263" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -16287,8 +16586,9 @@
       <c r="AU263" s="1"/>
       <c r="AV263" s="1"/>
       <c r="AW263" s="1"/>
-    </row>
-    <row r="264" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX263" s="1"/>
+    </row>
+    <row r="264" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -16338,8 +16638,9 @@
       <c r="AU264" s="1"/>
       <c r="AV264" s="1"/>
       <c r="AW264" s="1"/>
-    </row>
-    <row r="265" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX264" s="1"/>
+    </row>
+    <row r="265" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -16389,8 +16690,9 @@
       <c r="AU265" s="1"/>
       <c r="AV265" s="1"/>
       <c r="AW265" s="1"/>
-    </row>
-    <row r="266" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX265" s="1"/>
+    </row>
+    <row r="266" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -16440,8 +16742,9 @@
       <c r="AU266" s="1"/>
       <c r="AV266" s="1"/>
       <c r="AW266" s="1"/>
-    </row>
-    <row r="267" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX266" s="1"/>
+    </row>
+    <row r="267" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -16491,8 +16794,9 @@
       <c r="AU267" s="1"/>
       <c r="AV267" s="1"/>
       <c r="AW267" s="1"/>
-    </row>
-    <row r="268" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX267" s="1"/>
+    </row>
+    <row r="268" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -16542,8 +16846,9 @@
       <c r="AU268" s="1"/>
       <c r="AV268" s="1"/>
       <c r="AW268" s="1"/>
-    </row>
-    <row r="269" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX268" s="1"/>
+    </row>
+    <row r="269" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -16593,8 +16898,9 @@
       <c r="AU269" s="1"/>
       <c r="AV269" s="1"/>
       <c r="AW269" s="1"/>
-    </row>
-    <row r="270" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX269" s="1"/>
+    </row>
+    <row r="270" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -16644,8 +16950,9 @@
       <c r="AU270" s="1"/>
       <c r="AV270" s="1"/>
       <c r="AW270" s="1"/>
-    </row>
-    <row r="271" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX270" s="1"/>
+    </row>
+    <row r="271" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -16695,8 +17002,9 @@
       <c r="AU271" s="1"/>
       <c r="AV271" s="1"/>
       <c r="AW271" s="1"/>
-    </row>
-    <row r="272" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX271" s="1"/>
+    </row>
+    <row r="272" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -16746,8 +17054,9 @@
       <c r="AU272" s="1"/>
       <c r="AV272" s="1"/>
       <c r="AW272" s="1"/>
-    </row>
-    <row r="273" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX272" s="1"/>
+    </row>
+    <row r="273" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -16797,8 +17106,9 @@
       <c r="AU273" s="1"/>
       <c r="AV273" s="1"/>
       <c r="AW273" s="1"/>
-    </row>
-    <row r="274" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX273" s="1"/>
+    </row>
+    <row r="274" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -16848,8 +17158,9 @@
       <c r="AU274" s="1"/>
       <c r="AV274" s="1"/>
       <c r="AW274" s="1"/>
-    </row>
-    <row r="275" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX274" s="1"/>
+    </row>
+    <row r="275" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -16899,8 +17210,9 @@
       <c r="AU275" s="1"/>
       <c r="AV275" s="1"/>
       <c r="AW275" s="1"/>
-    </row>
-    <row r="276" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX275" s="1"/>
+    </row>
+    <row r="276" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -16950,8 +17262,9 @@
       <c r="AU276" s="1"/>
       <c r="AV276" s="1"/>
       <c r="AW276" s="1"/>
-    </row>
-    <row r="277" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX276" s="1"/>
+    </row>
+    <row r="277" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -17001,8 +17314,9 @@
       <c r="AU277" s="1"/>
       <c r="AV277" s="1"/>
       <c r="AW277" s="1"/>
-    </row>
-    <row r="278" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX277" s="1"/>
+    </row>
+    <row r="278" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -17052,8 +17366,9 @@
       <c r="AU278" s="1"/>
       <c r="AV278" s="1"/>
       <c r="AW278" s="1"/>
-    </row>
-    <row r="279" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX278" s="1"/>
+    </row>
+    <row r="279" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -17103,8 +17418,9 @@
       <c r="AU279" s="1"/>
       <c r="AV279" s="1"/>
       <c r="AW279" s="1"/>
-    </row>
-    <row r="280" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX279" s="1"/>
+    </row>
+    <row r="280" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -17154,8 +17470,9 @@
       <c r="AU280" s="1"/>
       <c r="AV280" s="1"/>
       <c r="AW280" s="1"/>
-    </row>
-    <row r="281" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX280" s="1"/>
+    </row>
+    <row r="281" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -17205,8 +17522,9 @@
       <c r="AU281" s="1"/>
       <c r="AV281" s="1"/>
       <c r="AW281" s="1"/>
-    </row>
-    <row r="282" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX281" s="1"/>
+    </row>
+    <row r="282" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -17256,8 +17574,9 @@
       <c r="AU282" s="1"/>
       <c r="AV282" s="1"/>
       <c r="AW282" s="1"/>
-    </row>
-    <row r="283" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX282" s="1"/>
+    </row>
+    <row r="283" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -17307,8 +17626,9 @@
       <c r="AU283" s="1"/>
       <c r="AV283" s="1"/>
       <c r="AW283" s="1"/>
-    </row>
-    <row r="284" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX283" s="1"/>
+    </row>
+    <row r="284" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -17358,8 +17678,9 @@
       <c r="AU284" s="1"/>
       <c r="AV284" s="1"/>
       <c r="AW284" s="1"/>
-    </row>
-    <row r="285" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX284" s="1"/>
+    </row>
+    <row r="285" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -17409,8 +17730,9 @@
       <c r="AU285" s="1"/>
       <c r="AV285" s="1"/>
       <c r="AW285" s="1"/>
-    </row>
-    <row r="286" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX285" s="1"/>
+    </row>
+    <row r="286" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -17460,8 +17782,9 @@
       <c r="AU286" s="1"/>
       <c r="AV286" s="1"/>
       <c r="AW286" s="1"/>
-    </row>
-    <row r="287" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX286" s="1"/>
+    </row>
+    <row r="287" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -17511,8 +17834,9 @@
       <c r="AU287" s="1"/>
       <c r="AV287" s="1"/>
       <c r="AW287" s="1"/>
-    </row>
-    <row r="288" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX287" s="1"/>
+    </row>
+    <row r="288" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -17562,8 +17886,9 @@
       <c r="AU288" s="1"/>
       <c r="AV288" s="1"/>
       <c r="AW288" s="1"/>
-    </row>
-    <row r="289" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX288" s="1"/>
+    </row>
+    <row r="289" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -17613,8 +17938,9 @@
       <c r="AU289" s="1"/>
       <c r="AV289" s="1"/>
       <c r="AW289" s="1"/>
-    </row>
-    <row r="290" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX289" s="1"/>
+    </row>
+    <row r="290" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -17664,8 +17990,9 @@
       <c r="AU290" s="1"/>
       <c r="AV290" s="1"/>
       <c r="AW290" s="1"/>
-    </row>
-    <row r="291" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX290" s="1"/>
+    </row>
+    <row r="291" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -17715,8 +18042,9 @@
       <c r="AU291" s="1"/>
       <c r="AV291" s="1"/>
       <c r="AW291" s="1"/>
-    </row>
-    <row r="292" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX291" s="1"/>
+    </row>
+    <row r="292" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -17766,8 +18094,9 @@
       <c r="AU292" s="1"/>
       <c r="AV292" s="1"/>
       <c r="AW292" s="1"/>
-    </row>
-    <row r="293" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX292" s="1"/>
+    </row>
+    <row r="293" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -17817,8 +18146,9 @@
       <c r="AU293" s="1"/>
       <c r="AV293" s="1"/>
       <c r="AW293" s="1"/>
-    </row>
-    <row r="294" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX293" s="1"/>
+    </row>
+    <row r="294" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -17868,8 +18198,9 @@
       <c r="AU294" s="1"/>
       <c r="AV294" s="1"/>
       <c r="AW294" s="1"/>
-    </row>
-    <row r="295" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX294" s="1"/>
+    </row>
+    <row r="295" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -17919,8 +18250,9 @@
       <c r="AU295" s="1"/>
       <c r="AV295" s="1"/>
       <c r="AW295" s="1"/>
-    </row>
-    <row r="296" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX295" s="1"/>
+    </row>
+    <row r="296" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -17970,8 +18302,9 @@
       <c r="AU296" s="1"/>
       <c r="AV296" s="1"/>
       <c r="AW296" s="1"/>
-    </row>
-    <row r="297" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX296" s="1"/>
+    </row>
+    <row r="297" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -18021,8 +18354,9 @@
       <c r="AU297" s="1"/>
       <c r="AV297" s="1"/>
       <c r="AW297" s="1"/>
-    </row>
-    <row r="298" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX297" s="1"/>
+    </row>
+    <row r="298" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -18072,8 +18406,9 @@
       <c r="AU298" s="1"/>
       <c r="AV298" s="1"/>
       <c r="AW298" s="1"/>
-    </row>
-    <row r="299" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX298" s="1"/>
+    </row>
+    <row r="299" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -18123,8 +18458,9 @@
       <c r="AU299" s="1"/>
       <c r="AV299" s="1"/>
       <c r="AW299" s="1"/>
-    </row>
-    <row r="300" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX299" s="1"/>
+    </row>
+    <row r="300" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -18174,8 +18510,9 @@
       <c r="AU300" s="1"/>
       <c r="AV300" s="1"/>
       <c r="AW300" s="1"/>
-    </row>
-    <row r="301" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX300" s="1"/>
+    </row>
+    <row r="301" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -18225,8 +18562,9 @@
       <c r="AU301" s="1"/>
       <c r="AV301" s="1"/>
       <c r="AW301" s="1"/>
-    </row>
-    <row r="302" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX301" s="1"/>
+    </row>
+    <row r="302" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -18276,8 +18614,9 @@
       <c r="AU302" s="1"/>
       <c r="AV302" s="1"/>
       <c r="AW302" s="1"/>
-    </row>
-    <row r="303" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX302" s="1"/>
+    </row>
+    <row r="303" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -18327,8 +18666,9 @@
       <c r="AU303" s="1"/>
       <c r="AV303" s="1"/>
       <c r="AW303" s="1"/>
-    </row>
-    <row r="304" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX303" s="1"/>
+    </row>
+    <row r="304" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -18378,8 +18718,9 @@
       <c r="AU304" s="1"/>
       <c r="AV304" s="1"/>
       <c r="AW304" s="1"/>
-    </row>
-    <row r="305" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX304" s="1"/>
+    </row>
+    <row r="305" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -18429,8 +18770,9 @@
       <c r="AU305" s="1"/>
       <c r="AV305" s="1"/>
       <c r="AW305" s="1"/>
-    </row>
-    <row r="306" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX305" s="1"/>
+    </row>
+    <row r="306" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -18480,8 +18822,9 @@
       <c r="AU306" s="1"/>
       <c r="AV306" s="1"/>
       <c r="AW306" s="1"/>
-    </row>
-    <row r="307" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX306" s="1"/>
+    </row>
+    <row r="307" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -18531,8 +18874,9 @@
       <c r="AU307" s="1"/>
       <c r="AV307" s="1"/>
       <c r="AW307" s="1"/>
-    </row>
-    <row r="308" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX307" s="1"/>
+    </row>
+    <row r="308" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -18582,8 +18926,9 @@
       <c r="AU308" s="1"/>
       <c r="AV308" s="1"/>
       <c r="AW308" s="1"/>
-    </row>
-    <row r="309" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX308" s="1"/>
+    </row>
+    <row r="309" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -18633,8 +18978,9 @@
       <c r="AU309" s="1"/>
       <c r="AV309" s="1"/>
       <c r="AW309" s="1"/>
-    </row>
-    <row r="310" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX309" s="1"/>
+    </row>
+    <row r="310" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -18684,8 +19030,9 @@
       <c r="AU310" s="1"/>
       <c r="AV310" s="1"/>
       <c r="AW310" s="1"/>
-    </row>
-    <row r="311" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX310" s="1"/>
+    </row>
+    <row r="311" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -18735,8 +19082,9 @@
       <c r="AU311" s="1"/>
       <c r="AV311" s="1"/>
       <c r="AW311" s="1"/>
-    </row>
-    <row r="312" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX311" s="1"/>
+    </row>
+    <row r="312" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -18786,8 +19134,9 @@
       <c r="AU312" s="1"/>
       <c r="AV312" s="1"/>
       <c r="AW312" s="1"/>
-    </row>
-    <row r="313" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX312" s="1"/>
+    </row>
+    <row r="313" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -18837,8 +19186,9 @@
       <c r="AU313" s="1"/>
       <c r="AV313" s="1"/>
       <c r="AW313" s="1"/>
-    </row>
-    <row r="314" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX313" s="1"/>
+    </row>
+    <row r="314" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -18888,8 +19238,9 @@
       <c r="AU314" s="1"/>
       <c r="AV314" s="1"/>
       <c r="AW314" s="1"/>
-    </row>
-    <row r="315" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX314" s="1"/>
+    </row>
+    <row r="315" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -18939,8 +19290,9 @@
       <c r="AU315" s="1"/>
       <c r="AV315" s="1"/>
       <c r="AW315" s="1"/>
-    </row>
-    <row r="316" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX315" s="1"/>
+    </row>
+    <row r="316" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -18990,8 +19342,9 @@
       <c r="AU316" s="1"/>
       <c r="AV316" s="1"/>
       <c r="AW316" s="1"/>
-    </row>
-    <row r="317" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX316" s="1"/>
+    </row>
+    <row r="317" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -19041,8 +19394,9 @@
       <c r="AU317" s="1"/>
       <c r="AV317" s="1"/>
       <c r="AW317" s="1"/>
-    </row>
-    <row r="318" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX317" s="1"/>
+    </row>
+    <row r="318" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -19092,8 +19446,9 @@
       <c r="AU318" s="1"/>
       <c r="AV318" s="1"/>
       <c r="AW318" s="1"/>
-    </row>
-    <row r="319" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX318" s="1"/>
+    </row>
+    <row r="319" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -19143,8 +19498,9 @@
       <c r="AU319" s="1"/>
       <c r="AV319" s="1"/>
       <c r="AW319" s="1"/>
-    </row>
-    <row r="320" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX319" s="1"/>
+    </row>
+    <row r="320" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -19194,8 +19550,9 @@
       <c r="AU320" s="1"/>
       <c r="AV320" s="1"/>
       <c r="AW320" s="1"/>
-    </row>
-    <row r="321" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX320" s="1"/>
+    </row>
+    <row r="321" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -19245,8 +19602,9 @@
       <c r="AU321" s="1"/>
       <c r="AV321" s="1"/>
       <c r="AW321" s="1"/>
-    </row>
-    <row r="322" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX321" s="1"/>
+    </row>
+    <row r="322" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -19296,8 +19654,9 @@
       <c r="AU322" s="1"/>
       <c r="AV322" s="1"/>
       <c r="AW322" s="1"/>
-    </row>
-    <row r="323" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX322" s="1"/>
+    </row>
+    <row r="323" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -19347,8 +19706,9 @@
       <c r="AU323" s="1"/>
       <c r="AV323" s="1"/>
       <c r="AW323" s="1"/>
-    </row>
-    <row r="324" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX323" s="1"/>
+    </row>
+    <row r="324" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -19398,8 +19758,9 @@
       <c r="AU324" s="1"/>
       <c r="AV324" s="1"/>
       <c r="AW324" s="1"/>
-    </row>
-    <row r="325" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX324" s="1"/>
+    </row>
+    <row r="325" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -19449,8 +19810,9 @@
       <c r="AU325" s="1"/>
       <c r="AV325" s="1"/>
       <c r="AW325" s="1"/>
-    </row>
-    <row r="326" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX325" s="1"/>
+    </row>
+    <row r="326" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -19500,8 +19862,9 @@
       <c r="AU326" s="1"/>
       <c r="AV326" s="1"/>
       <c r="AW326" s="1"/>
-    </row>
-    <row r="327" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX326" s="1"/>
+    </row>
+    <row r="327" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -19551,8 +19914,9 @@
       <c r="AU327" s="1"/>
       <c r="AV327" s="1"/>
       <c r="AW327" s="1"/>
-    </row>
-    <row r="328" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX327" s="1"/>
+    </row>
+    <row r="328" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -19602,8 +19966,9 @@
       <c r="AU328" s="1"/>
       <c r="AV328" s="1"/>
       <c r="AW328" s="1"/>
-    </row>
-    <row r="329" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX328" s="1"/>
+    </row>
+    <row r="329" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -19653,8 +20018,9 @@
       <c r="AU329" s="1"/>
       <c r="AV329" s="1"/>
       <c r="AW329" s="1"/>
-    </row>
-    <row r="330" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX329" s="1"/>
+    </row>
+    <row r="330" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -19704,8 +20070,9 @@
       <c r="AU330" s="1"/>
       <c r="AV330" s="1"/>
       <c r="AW330" s="1"/>
-    </row>
-    <row r="331" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX330" s="1"/>
+    </row>
+    <row r="331" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -19755,8 +20122,9 @@
       <c r="AU331" s="1"/>
       <c r="AV331" s="1"/>
       <c r="AW331" s="1"/>
-    </row>
-    <row r="332" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX331" s="1"/>
+    </row>
+    <row r="332" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -19806,8 +20174,9 @@
       <c r="AU332" s="1"/>
       <c r="AV332" s="1"/>
       <c r="AW332" s="1"/>
-    </row>
-    <row r="333" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX332" s="1"/>
+    </row>
+    <row r="333" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -19857,8 +20226,9 @@
       <c r="AU333" s="1"/>
       <c r="AV333" s="1"/>
       <c r="AW333" s="1"/>
-    </row>
-    <row r="334" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX333" s="1"/>
+    </row>
+    <row r="334" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -19908,8 +20278,9 @@
       <c r="AU334" s="1"/>
       <c r="AV334" s="1"/>
       <c r="AW334" s="1"/>
-    </row>
-    <row r="335" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX334" s="1"/>
+    </row>
+    <row r="335" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -19959,8 +20330,9 @@
       <c r="AU335" s="1"/>
       <c r="AV335" s="1"/>
       <c r="AW335" s="1"/>
-    </row>
-    <row r="336" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX335" s="1"/>
+    </row>
+    <row r="336" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -20010,8 +20382,9 @@
       <c r="AU336" s="1"/>
       <c r="AV336" s="1"/>
       <c r="AW336" s="1"/>
-    </row>
-    <row r="337" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX336" s="1"/>
+    </row>
+    <row r="337" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -20061,8 +20434,9 @@
       <c r="AU337" s="1"/>
       <c r="AV337" s="1"/>
       <c r="AW337" s="1"/>
-    </row>
-    <row r="338" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX337" s="1"/>
+    </row>
+    <row r="338" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -20112,8 +20486,9 @@
       <c r="AU338" s="1"/>
       <c r="AV338" s="1"/>
       <c r="AW338" s="1"/>
-    </row>
-    <row r="339" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX338" s="1"/>
+    </row>
+    <row r="339" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -20163,8 +20538,9 @@
       <c r="AU339" s="1"/>
       <c r="AV339" s="1"/>
       <c r="AW339" s="1"/>
-    </row>
-    <row r="340" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX339" s="1"/>
+    </row>
+    <row r="340" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -20214,8 +20590,9 @@
       <c r="AU340" s="1"/>
       <c r="AV340" s="1"/>
       <c r="AW340" s="1"/>
-    </row>
-    <row r="341" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX340" s="1"/>
+    </row>
+    <row r="341" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -20265,8 +20642,9 @@
       <c r="AU341" s="1"/>
       <c r="AV341" s="1"/>
       <c r="AW341" s="1"/>
-    </row>
-    <row r="342" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX341" s="1"/>
+    </row>
+    <row r="342" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -20316,8 +20694,9 @@
       <c r="AU342" s="1"/>
       <c r="AV342" s="1"/>
       <c r="AW342" s="1"/>
-    </row>
-    <row r="343" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX342" s="1"/>
+    </row>
+    <row r="343" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -20367,8 +20746,9 @@
       <c r="AU343" s="1"/>
       <c r="AV343" s="1"/>
       <c r="AW343" s="1"/>
-    </row>
-    <row r="344" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX343" s="1"/>
+    </row>
+    <row r="344" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -20418,8 +20798,9 @@
       <c r="AU344" s="1"/>
       <c r="AV344" s="1"/>
       <c r="AW344" s="1"/>
-    </row>
-    <row r="345" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX344" s="1"/>
+    </row>
+    <row r="345" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -20469,8 +20850,9 @@
       <c r="AU345" s="1"/>
       <c r="AV345" s="1"/>
       <c r="AW345" s="1"/>
-    </row>
-    <row r="346" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX345" s="1"/>
+    </row>
+    <row r="346" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -20520,8 +20902,9 @@
       <c r="AU346" s="1"/>
       <c r="AV346" s="1"/>
       <c r="AW346" s="1"/>
-    </row>
-    <row r="347" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX346" s="1"/>
+    </row>
+    <row r="347" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -20571,8 +20954,9 @@
       <c r="AU347" s="1"/>
       <c r="AV347" s="1"/>
       <c r="AW347" s="1"/>
-    </row>
-    <row r="348" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX347" s="1"/>
+    </row>
+    <row r="348" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -20622,8 +21006,9 @@
       <c r="AU348" s="1"/>
       <c r="AV348" s="1"/>
       <c r="AW348" s="1"/>
-    </row>
-    <row r="349" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX348" s="1"/>
+    </row>
+    <row r="349" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -20673,8 +21058,9 @@
       <c r="AU349" s="1"/>
       <c r="AV349" s="1"/>
       <c r="AW349" s="1"/>
-    </row>
-    <row r="350" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX349" s="1"/>
+    </row>
+    <row r="350" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -20724,8 +21110,9 @@
       <c r="AU350" s="1"/>
       <c r="AV350" s="1"/>
       <c r="AW350" s="1"/>
-    </row>
-    <row r="351" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX350" s="1"/>
+    </row>
+    <row r="351" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -20775,8 +21162,9 @@
       <c r="AU351" s="1"/>
       <c r="AV351" s="1"/>
       <c r="AW351" s="1"/>
-    </row>
-    <row r="352" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX351" s="1"/>
+    </row>
+    <row r="352" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -20826,8 +21214,9 @@
       <c r="AU352" s="1"/>
       <c r="AV352" s="1"/>
       <c r="AW352" s="1"/>
-    </row>
-    <row r="353" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX352" s="1"/>
+    </row>
+    <row r="353" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -20877,8 +21266,9 @@
       <c r="AU353" s="1"/>
       <c r="AV353" s="1"/>
       <c r="AW353" s="1"/>
-    </row>
-    <row r="354" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX353" s="1"/>
+    </row>
+    <row r="354" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -20928,8 +21318,9 @@
       <c r="AU354" s="1"/>
       <c r="AV354" s="1"/>
       <c r="AW354" s="1"/>
-    </row>
-    <row r="355" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX354" s="1"/>
+    </row>
+    <row r="355" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -20979,8 +21370,9 @@
       <c r="AU355" s="1"/>
       <c r="AV355" s="1"/>
       <c r="AW355" s="1"/>
-    </row>
-    <row r="356" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX355" s="1"/>
+    </row>
+    <row r="356" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -21030,8 +21422,9 @@
       <c r="AU356" s="1"/>
       <c r="AV356" s="1"/>
       <c r="AW356" s="1"/>
-    </row>
-    <row r="357" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX356" s="1"/>
+    </row>
+    <row r="357" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -21081,8 +21474,9 @@
       <c r="AU357" s="1"/>
       <c r="AV357" s="1"/>
       <c r="AW357" s="1"/>
-    </row>
-    <row r="358" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX357" s="1"/>
+    </row>
+    <row r="358" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -21132,8 +21526,9 @@
       <c r="AU358" s="1"/>
       <c r="AV358" s="1"/>
       <c r="AW358" s="1"/>
-    </row>
-    <row r="359" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX358" s="1"/>
+    </row>
+    <row r="359" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -21183,8 +21578,9 @@
       <c r="AU359" s="1"/>
       <c r="AV359" s="1"/>
       <c r="AW359" s="1"/>
-    </row>
-    <row r="360" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX359" s="1"/>
+    </row>
+    <row r="360" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -21234,8 +21630,9 @@
       <c r="AU360" s="1"/>
       <c r="AV360" s="1"/>
       <c r="AW360" s="1"/>
-    </row>
-    <row r="361" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX360" s="1"/>
+    </row>
+    <row r="361" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -21285,8 +21682,9 @@
       <c r="AU361" s="1"/>
       <c r="AV361" s="1"/>
       <c r="AW361" s="1"/>
-    </row>
-    <row r="362" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX361" s="1"/>
+    </row>
+    <row r="362" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -21336,8 +21734,9 @@
       <c r="AU362" s="1"/>
       <c r="AV362" s="1"/>
       <c r="AW362" s="1"/>
-    </row>
-    <row r="363" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX362" s="1"/>
+    </row>
+    <row r="363" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -21387,8 +21786,9 @@
       <c r="AU363" s="1"/>
       <c r="AV363" s="1"/>
       <c r="AW363" s="1"/>
-    </row>
-    <row r="364" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX363" s="1"/>
+    </row>
+    <row r="364" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -21438,8 +21838,9 @@
       <c r="AU364" s="1"/>
       <c r="AV364" s="1"/>
       <c r="AW364" s="1"/>
-    </row>
-    <row r="365" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX364" s="1"/>
+    </row>
+    <row r="365" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -21489,8 +21890,9 @@
       <c r="AU365" s="1"/>
       <c r="AV365" s="1"/>
       <c r="AW365" s="1"/>
-    </row>
-    <row r="366" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX365" s="1"/>
+    </row>
+    <row r="366" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -21540,8 +21942,9 @@
       <c r="AU366" s="1"/>
       <c r="AV366" s="1"/>
       <c r="AW366" s="1"/>
-    </row>
-    <row r="367" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX366" s="1"/>
+    </row>
+    <row r="367" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -21591,8 +21994,9 @@
       <c r="AU367" s="1"/>
       <c r="AV367" s="1"/>
       <c r="AW367" s="1"/>
-    </row>
-    <row r="368" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX367" s="1"/>
+    </row>
+    <row r="368" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -21642,8 +22046,9 @@
       <c r="AU368" s="1"/>
       <c r="AV368" s="1"/>
       <c r="AW368" s="1"/>
-    </row>
-    <row r="369" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX368" s="1"/>
+    </row>
+    <row r="369" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -21693,8 +22098,9 @@
       <c r="AU369" s="1"/>
       <c r="AV369" s="1"/>
       <c r="AW369" s="1"/>
-    </row>
-    <row r="370" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX369" s="1"/>
+    </row>
+    <row r="370" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -21744,8 +22150,9 @@
       <c r="AU370" s="1"/>
       <c r="AV370" s="1"/>
       <c r="AW370" s="1"/>
-    </row>
-    <row r="371" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX370" s="1"/>
+    </row>
+    <row r="371" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -21795,8 +22202,9 @@
       <c r="AU371" s="1"/>
       <c r="AV371" s="1"/>
       <c r="AW371" s="1"/>
-    </row>
-    <row r="372" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX371" s="1"/>
+    </row>
+    <row r="372" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -21846,8 +22254,9 @@
       <c r="AU372" s="1"/>
       <c r="AV372" s="1"/>
       <c r="AW372" s="1"/>
-    </row>
-    <row r="373" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX372" s="1"/>
+    </row>
+    <row r="373" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -21897,8 +22306,9 @@
       <c r="AU373" s="1"/>
       <c r="AV373" s="1"/>
       <c r="AW373" s="1"/>
-    </row>
-    <row r="374" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX373" s="1"/>
+    </row>
+    <row r="374" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -21948,8 +22358,9 @@
       <c r="AU374" s="1"/>
       <c r="AV374" s="1"/>
       <c r="AW374" s="1"/>
-    </row>
-    <row r="375" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX374" s="1"/>
+    </row>
+    <row r="375" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -21999,8 +22410,9 @@
       <c r="AU375" s="1"/>
       <c r="AV375" s="1"/>
       <c r="AW375" s="1"/>
-    </row>
-    <row r="376" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX375" s="1"/>
+    </row>
+    <row r="376" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -22050,8 +22462,9 @@
       <c r="AU376" s="1"/>
       <c r="AV376" s="1"/>
       <c r="AW376" s="1"/>
-    </row>
-    <row r="377" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX376" s="1"/>
+    </row>
+    <row r="377" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -22101,8 +22514,9 @@
       <c r="AU377" s="1"/>
       <c r="AV377" s="1"/>
       <c r="AW377" s="1"/>
-    </row>
-    <row r="378" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX377" s="1"/>
+    </row>
+    <row r="378" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -22152,8 +22566,9 @@
       <c r="AU378" s="1"/>
       <c r="AV378" s="1"/>
       <c r="AW378" s="1"/>
-    </row>
-    <row r="379" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX378" s="1"/>
+    </row>
+    <row r="379" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -22203,8 +22618,9 @@
       <c r="AU379" s="1"/>
       <c r="AV379" s="1"/>
       <c r="AW379" s="1"/>
-    </row>
-    <row r="380" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX379" s="1"/>
+    </row>
+    <row r="380" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -22254,8 +22670,9 @@
       <c r="AU380" s="1"/>
       <c r="AV380" s="1"/>
       <c r="AW380" s="1"/>
-    </row>
-    <row r="381" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX380" s="1"/>
+    </row>
+    <row r="381" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -22305,8 +22722,9 @@
       <c r="AU381" s="1"/>
       <c r="AV381" s="1"/>
       <c r="AW381" s="1"/>
-    </row>
-    <row r="382" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX381" s="1"/>
+    </row>
+    <row r="382" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -22356,8 +22774,9 @@
       <c r="AU382" s="1"/>
       <c r="AV382" s="1"/>
       <c r="AW382" s="1"/>
-    </row>
-    <row r="383" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX382" s="1"/>
+    </row>
+    <row r="383" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -22407,8 +22826,9 @@
       <c r="AU383" s="1"/>
       <c r="AV383" s="1"/>
       <c r="AW383" s="1"/>
-    </row>
-    <row r="384" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX383" s="1"/>
+    </row>
+    <row r="384" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -22458,8 +22878,9 @@
       <c r="AU384" s="1"/>
       <c r="AV384" s="1"/>
       <c r="AW384" s="1"/>
-    </row>
-    <row r="385" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX384" s="1"/>
+    </row>
+    <row r="385" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -22509,8 +22930,9 @@
       <c r="AU385" s="1"/>
       <c r="AV385" s="1"/>
       <c r="AW385" s="1"/>
-    </row>
-    <row r="386" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX385" s="1"/>
+    </row>
+    <row r="386" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -22560,8 +22982,9 @@
       <c r="AU386" s="1"/>
       <c r="AV386" s="1"/>
       <c r="AW386" s="1"/>
-    </row>
-    <row r="387" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX386" s="1"/>
+    </row>
+    <row r="387" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -22611,8 +23034,9 @@
       <c r="AU387" s="1"/>
       <c r="AV387" s="1"/>
       <c r="AW387" s="1"/>
-    </row>
-    <row r="388" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX387" s="1"/>
+    </row>
+    <row r="388" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -22662,8 +23086,9 @@
       <c r="AU388" s="1"/>
       <c r="AV388" s="1"/>
       <c r="AW388" s="1"/>
-    </row>
-    <row r="389" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX388" s="1"/>
+    </row>
+    <row r="389" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -22713,8 +23138,9 @@
       <c r="AU389" s="1"/>
       <c r="AV389" s="1"/>
       <c r="AW389" s="1"/>
-    </row>
-    <row r="390" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX389" s="1"/>
+    </row>
+    <row r="390" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -22764,8 +23190,9 @@
       <c r="AU390" s="1"/>
       <c r="AV390" s="1"/>
       <c r="AW390" s="1"/>
-    </row>
-    <row r="391" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX390" s="1"/>
+    </row>
+    <row r="391" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -22815,8 +23242,9 @@
       <c r="AU391" s="1"/>
       <c r="AV391" s="1"/>
       <c r="AW391" s="1"/>
-    </row>
-    <row r="392" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX391" s="1"/>
+    </row>
+    <row r="392" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -22866,8 +23294,9 @@
       <c r="AU392" s="1"/>
       <c r="AV392" s="1"/>
       <c r="AW392" s="1"/>
-    </row>
-    <row r="393" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX392" s="1"/>
+    </row>
+    <row r="393" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -22917,8 +23346,9 @@
       <c r="AU393" s="1"/>
       <c r="AV393" s="1"/>
       <c r="AW393" s="1"/>
-    </row>
-    <row r="394" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX393" s="1"/>
+    </row>
+    <row r="394" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -22968,8 +23398,9 @@
       <c r="AU394" s="1"/>
       <c r="AV394" s="1"/>
       <c r="AW394" s="1"/>
-    </row>
-    <row r="395" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX394" s="1"/>
+    </row>
+    <row r="395" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -23019,8 +23450,9 @@
       <c r="AU395" s="1"/>
       <c r="AV395" s="1"/>
       <c r="AW395" s="1"/>
-    </row>
-    <row r="396" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX395" s="1"/>
+    </row>
+    <row r="396" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -23070,8 +23502,9 @@
       <c r="AU396" s="1"/>
       <c r="AV396" s="1"/>
       <c r="AW396" s="1"/>
-    </row>
-    <row r="397" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX396" s="1"/>
+    </row>
+    <row r="397" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -23121,8 +23554,9 @@
       <c r="AU397" s="1"/>
       <c r="AV397" s="1"/>
       <c r="AW397" s="1"/>
-    </row>
-    <row r="398" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX397" s="1"/>
+    </row>
+    <row r="398" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -23172,8 +23606,9 @@
       <c r="AU398" s="1"/>
       <c r="AV398" s="1"/>
       <c r="AW398" s="1"/>
-    </row>
-    <row r="399" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX398" s="1"/>
+    </row>
+    <row r="399" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -23223,8 +23658,9 @@
       <c r="AU399" s="1"/>
       <c r="AV399" s="1"/>
       <c r="AW399" s="1"/>
-    </row>
-    <row r="400" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX399" s="1"/>
+    </row>
+    <row r="400" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -23274,8 +23710,9 @@
       <c r="AU400" s="1"/>
       <c r="AV400" s="1"/>
       <c r="AW400" s="1"/>
-    </row>
-    <row r="401" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX400" s="1"/>
+    </row>
+    <row r="401" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -23325,8 +23762,9 @@
       <c r="AU401" s="1"/>
       <c r="AV401" s="1"/>
       <c r="AW401" s="1"/>
-    </row>
-    <row r="402" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX401" s="1"/>
+    </row>
+    <row r="402" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -23376,8 +23814,9 @@
       <c r="AU402" s="1"/>
       <c r="AV402" s="1"/>
       <c r="AW402" s="1"/>
-    </row>
-    <row r="403" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX402" s="1"/>
+    </row>
+    <row r="403" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -23427,8 +23866,9 @@
       <c r="AU403" s="1"/>
       <c r="AV403" s="1"/>
       <c r="AW403" s="1"/>
-    </row>
-    <row r="404" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX403" s="1"/>
+    </row>
+    <row r="404" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -23478,8 +23918,9 @@
       <c r="AU404" s="1"/>
       <c r="AV404" s="1"/>
       <c r="AW404" s="1"/>
-    </row>
-    <row r="405" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX404" s="1"/>
+    </row>
+    <row r="405" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -23529,8 +23970,9 @@
       <c r="AU405" s="1"/>
       <c r="AV405" s="1"/>
       <c r="AW405" s="1"/>
-    </row>
-    <row r="406" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX405" s="1"/>
+    </row>
+    <row r="406" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -23580,8 +24022,9 @@
       <c r="AU406" s="1"/>
       <c r="AV406" s="1"/>
       <c r="AW406" s="1"/>
-    </row>
-    <row r="407" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX406" s="1"/>
+    </row>
+    <row r="407" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -23631,8 +24074,9 @@
       <c r="AU407" s="1"/>
       <c r="AV407" s="1"/>
       <c r="AW407" s="1"/>
-    </row>
-    <row r="408" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX407" s="1"/>
+    </row>
+    <row r="408" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -23682,8 +24126,9 @@
       <c r="AU408" s="1"/>
       <c r="AV408" s="1"/>
       <c r="AW408" s="1"/>
-    </row>
-    <row r="409" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX408" s="1"/>
+    </row>
+    <row r="409" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -23733,8 +24178,9 @@
       <c r="AU409" s="1"/>
       <c r="AV409" s="1"/>
       <c r="AW409" s="1"/>
-    </row>
-    <row r="410" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX409" s="1"/>
+    </row>
+    <row r="410" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -23784,8 +24230,9 @@
       <c r="AU410" s="1"/>
       <c r="AV410" s="1"/>
       <c r="AW410" s="1"/>
-    </row>
-    <row r="411" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX410" s="1"/>
+    </row>
+    <row r="411" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -23835,8 +24282,9 @@
       <c r="AU411" s="1"/>
       <c r="AV411" s="1"/>
       <c r="AW411" s="1"/>
-    </row>
-    <row r="412" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX411" s="1"/>
+    </row>
+    <row r="412" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -23886,8 +24334,9 @@
       <c r="AU412" s="1"/>
       <c r="AV412" s="1"/>
       <c r="AW412" s="1"/>
-    </row>
-    <row r="413" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX412" s="1"/>
+    </row>
+    <row r="413" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -23937,8 +24386,9 @@
       <c r="AU413" s="1"/>
       <c r="AV413" s="1"/>
       <c r="AW413" s="1"/>
-    </row>
-    <row r="414" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX413" s="1"/>
+    </row>
+    <row r="414" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -23988,8 +24438,9 @@
       <c r="AU414" s="1"/>
       <c r="AV414" s="1"/>
       <c r="AW414" s="1"/>
-    </row>
-    <row r="415" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX414" s="1"/>
+    </row>
+    <row r="415" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -24039,8 +24490,9 @@
       <c r="AU415" s="1"/>
       <c r="AV415" s="1"/>
       <c r="AW415" s="1"/>
-    </row>
-    <row r="416" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX415" s="1"/>
+    </row>
+    <row r="416" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -24090,8 +24542,9 @@
       <c r="AU416" s="1"/>
       <c r="AV416" s="1"/>
       <c r="AW416" s="1"/>
-    </row>
-    <row r="417" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX416" s="1"/>
+    </row>
+    <row r="417" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -24141,8 +24594,9 @@
       <c r="AU417" s="1"/>
       <c r="AV417" s="1"/>
       <c r="AW417" s="1"/>
-    </row>
-    <row r="418" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX417" s="1"/>
+    </row>
+    <row r="418" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -24192,8 +24646,9 @@
       <c r="AU418" s="1"/>
       <c r="AV418" s="1"/>
       <c r="AW418" s="1"/>
-    </row>
-    <row r="419" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX418" s="1"/>
+    </row>
+    <row r="419" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -24243,8 +24698,9 @@
       <c r="AU419" s="1"/>
       <c r="AV419" s="1"/>
       <c r="AW419" s="1"/>
-    </row>
-    <row r="420" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX419" s="1"/>
+    </row>
+    <row r="420" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -24294,8 +24750,9 @@
       <c r="AU420" s="1"/>
       <c r="AV420" s="1"/>
       <c r="AW420" s="1"/>
-    </row>
-    <row r="421" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX420" s="1"/>
+    </row>
+    <row r="421" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -24345,8 +24802,9 @@
       <c r="AU421" s="1"/>
       <c r="AV421" s="1"/>
       <c r="AW421" s="1"/>
-    </row>
-    <row r="422" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX421" s="1"/>
+    </row>
+    <row r="422" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -24396,8 +24854,9 @@
       <c r="AU422" s="1"/>
       <c r="AV422" s="1"/>
       <c r="AW422" s="1"/>
-    </row>
-    <row r="423" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX422" s="1"/>
+    </row>
+    <row r="423" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -24447,8 +24906,9 @@
       <c r="AU423" s="1"/>
       <c r="AV423" s="1"/>
       <c r="AW423" s="1"/>
-    </row>
-    <row r="424" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX423" s="1"/>
+    </row>
+    <row r="424" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -24498,8 +24958,9 @@
       <c r="AU424" s="1"/>
       <c r="AV424" s="1"/>
       <c r="AW424" s="1"/>
-    </row>
-    <row r="425" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX424" s="1"/>
+    </row>
+    <row r="425" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -24549,8 +25010,9 @@
       <c r="AU425" s="1"/>
       <c r="AV425" s="1"/>
       <c r="AW425" s="1"/>
-    </row>
-    <row r="426" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX425" s="1"/>
+    </row>
+    <row r="426" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -24600,8 +25062,9 @@
       <c r="AU426" s="1"/>
       <c r="AV426" s="1"/>
       <c r="AW426" s="1"/>
-    </row>
-    <row r="427" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX426" s="1"/>
+    </row>
+    <row r="427" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -24651,8 +25114,9 @@
       <c r="AU427" s="1"/>
       <c r="AV427" s="1"/>
       <c r="AW427" s="1"/>
-    </row>
-    <row r="428" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX427" s="1"/>
+    </row>
+    <row r="428" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -24702,8 +25166,9 @@
       <c r="AU428" s="1"/>
       <c r="AV428" s="1"/>
       <c r="AW428" s="1"/>
-    </row>
-    <row r="429" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX428" s="1"/>
+    </row>
+    <row r="429" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -24753,8 +25218,9 @@
       <c r="AU429" s="1"/>
       <c r="AV429" s="1"/>
       <c r="AW429" s="1"/>
-    </row>
-    <row r="430" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX429" s="1"/>
+    </row>
+    <row r="430" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -24804,8 +25270,9 @@
       <c r="AU430" s="1"/>
       <c r="AV430" s="1"/>
       <c r="AW430" s="1"/>
-    </row>
-    <row r="431" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX430" s="1"/>
+    </row>
+    <row r="431" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -24855,8 +25322,9 @@
       <c r="AU431" s="1"/>
       <c r="AV431" s="1"/>
       <c r="AW431" s="1"/>
-    </row>
-    <row r="432" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX431" s="1"/>
+    </row>
+    <row r="432" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -24906,8 +25374,9 @@
       <c r="AU432" s="1"/>
       <c r="AV432" s="1"/>
       <c r="AW432" s="1"/>
-    </row>
-    <row r="433" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX432" s="1"/>
+    </row>
+    <row r="433" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -24957,8 +25426,9 @@
       <c r="AU433" s="1"/>
       <c r="AV433" s="1"/>
       <c r="AW433" s="1"/>
-    </row>
-    <row r="434" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX433" s="1"/>
+    </row>
+    <row r="434" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -25008,8 +25478,9 @@
       <c r="AU434" s="1"/>
       <c r="AV434" s="1"/>
       <c r="AW434" s="1"/>
-    </row>
-    <row r="435" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX434" s="1"/>
+    </row>
+    <row r="435" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -25059,8 +25530,9 @@
       <c r="AU435" s="1"/>
       <c r="AV435" s="1"/>
       <c r="AW435" s="1"/>
-    </row>
-    <row r="436" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX435" s="1"/>
+    </row>
+    <row r="436" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -25110,8 +25582,9 @@
       <c r="AU436" s="1"/>
       <c r="AV436" s="1"/>
       <c r="AW436" s="1"/>
-    </row>
-    <row r="437" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX436" s="1"/>
+    </row>
+    <row r="437" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -25161,8 +25634,9 @@
       <c r="AU437" s="1"/>
       <c r="AV437" s="1"/>
       <c r="AW437" s="1"/>
-    </row>
-    <row r="438" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX437" s="1"/>
+    </row>
+    <row r="438" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -25212,8 +25686,9 @@
       <c r="AU438" s="1"/>
       <c r="AV438" s="1"/>
       <c r="AW438" s="1"/>
-    </row>
-    <row r="439" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX438" s="1"/>
+    </row>
+    <row r="439" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -25263,8 +25738,9 @@
       <c r="AU439" s="1"/>
       <c r="AV439" s="1"/>
       <c r="AW439" s="1"/>
-    </row>
-    <row r="440" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX439" s="1"/>
+    </row>
+    <row r="440" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -25314,8 +25790,9 @@
       <c r="AU440" s="1"/>
       <c r="AV440" s="1"/>
       <c r="AW440" s="1"/>
-    </row>
-    <row r="441" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX440" s="1"/>
+    </row>
+    <row r="441" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -25365,8 +25842,9 @@
       <c r="AU441" s="1"/>
       <c r="AV441" s="1"/>
       <c r="AW441" s="1"/>
-    </row>
-    <row r="442" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX441" s="1"/>
+    </row>
+    <row r="442" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -25416,8 +25894,9 @@
       <c r="AU442" s="1"/>
       <c r="AV442" s="1"/>
       <c r="AW442" s="1"/>
-    </row>
-    <row r="443" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX442" s="1"/>
+    </row>
+    <row r="443" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -25467,8 +25946,9 @@
       <c r="AU443" s="1"/>
       <c r="AV443" s="1"/>
       <c r="AW443" s="1"/>
-    </row>
-    <row r="444" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX443" s="1"/>
+    </row>
+    <row r="444" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -25518,8 +25998,9 @@
       <c r="AU444" s="1"/>
       <c r="AV444" s="1"/>
       <c r="AW444" s="1"/>
-    </row>
-    <row r="445" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX444" s="1"/>
+    </row>
+    <row r="445" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -25569,8 +26050,9 @@
       <c r="AU445" s="1"/>
       <c r="AV445" s="1"/>
       <c r="AW445" s="1"/>
-    </row>
-    <row r="446" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX445" s="1"/>
+    </row>
+    <row r="446" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -25620,8 +26102,9 @@
       <c r="AU446" s="1"/>
       <c r="AV446" s="1"/>
       <c r="AW446" s="1"/>
-    </row>
-    <row r="447" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX446" s="1"/>
+    </row>
+    <row r="447" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -25671,8 +26154,9 @@
       <c r="AU447" s="1"/>
       <c r="AV447" s="1"/>
       <c r="AW447" s="1"/>
-    </row>
-    <row r="448" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX447" s="1"/>
+    </row>
+    <row r="448" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -25722,8 +26206,9 @@
       <c r="AU448" s="1"/>
       <c r="AV448" s="1"/>
       <c r="AW448" s="1"/>
-    </row>
-    <row r="449" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX448" s="1"/>
+    </row>
+    <row r="449" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -25773,8 +26258,9 @@
       <c r="AU449" s="1"/>
       <c r="AV449" s="1"/>
       <c r="AW449" s="1"/>
-    </row>
-    <row r="450" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX449" s="1"/>
+    </row>
+    <row r="450" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -25824,8 +26310,9 @@
       <c r="AU450" s="1"/>
       <c r="AV450" s="1"/>
       <c r="AW450" s="1"/>
-    </row>
-    <row r="451" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX450" s="1"/>
+    </row>
+    <row r="451" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -25875,8 +26362,9 @@
       <c r="AU451" s="1"/>
       <c r="AV451" s="1"/>
       <c r="AW451" s="1"/>
-    </row>
-    <row r="452" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX451" s="1"/>
+    </row>
+    <row r="452" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -25926,8 +26414,9 @@
       <c r="AU452" s="1"/>
       <c r="AV452" s="1"/>
       <c r="AW452" s="1"/>
-    </row>
-    <row r="453" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX452" s="1"/>
+    </row>
+    <row r="453" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -25977,8 +26466,9 @@
       <c r="AU453" s="1"/>
       <c r="AV453" s="1"/>
       <c r="AW453" s="1"/>
-    </row>
-    <row r="454" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX453" s="1"/>
+    </row>
+    <row r="454" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -26028,8 +26518,9 @@
       <c r="AU454" s="1"/>
       <c r="AV454" s="1"/>
       <c r="AW454" s="1"/>
-    </row>
-    <row r="455" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX454" s="1"/>
+    </row>
+    <row r="455" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -26079,8 +26570,9 @@
       <c r="AU455" s="1"/>
       <c r="AV455" s="1"/>
       <c r="AW455" s="1"/>
-    </row>
-    <row r="456" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX455" s="1"/>
+    </row>
+    <row r="456" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -26130,8 +26622,9 @@
       <c r="AU456" s="1"/>
       <c r="AV456" s="1"/>
       <c r="AW456" s="1"/>
-    </row>
-    <row r="457" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX456" s="1"/>
+    </row>
+    <row r="457" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -26181,8 +26674,9 @@
       <c r="AU457" s="1"/>
       <c r="AV457" s="1"/>
       <c r="AW457" s="1"/>
-    </row>
-    <row r="458" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX457" s="1"/>
+    </row>
+    <row r="458" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -26232,8 +26726,9 @@
       <c r="AU458" s="1"/>
       <c r="AV458" s="1"/>
       <c r="AW458" s="1"/>
-    </row>
-    <row r="459" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX458" s="1"/>
+    </row>
+    <row r="459" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -26283,8 +26778,9 @@
       <c r="AU459" s="1"/>
       <c r="AV459" s="1"/>
       <c r="AW459" s="1"/>
-    </row>
-    <row r="460" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX459" s="1"/>
+    </row>
+    <row r="460" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -26334,8 +26830,9 @@
       <c r="AU460" s="1"/>
       <c r="AV460" s="1"/>
       <c r="AW460" s="1"/>
-    </row>
-    <row r="461" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX460" s="1"/>
+    </row>
+    <row r="461" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -26385,8 +26882,9 @@
       <c r="AU461" s="1"/>
       <c r="AV461" s="1"/>
       <c r="AW461" s="1"/>
-    </row>
-    <row r="462" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX461" s="1"/>
+    </row>
+    <row r="462" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -26436,8 +26934,9 @@
       <c r="AU462" s="1"/>
       <c r="AV462" s="1"/>
       <c r="AW462" s="1"/>
-    </row>
-    <row r="463" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX462" s="1"/>
+    </row>
+    <row r="463" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -26487,8 +26986,9 @@
       <c r="AU463" s="1"/>
       <c r="AV463" s="1"/>
       <c r="AW463" s="1"/>
-    </row>
-    <row r="464" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX463" s="1"/>
+    </row>
+    <row r="464" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -26538,8 +27038,9 @@
       <c r="AU464" s="1"/>
       <c r="AV464" s="1"/>
       <c r="AW464" s="1"/>
-    </row>
-    <row r="465" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX464" s="1"/>
+    </row>
+    <row r="465" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -26589,8 +27090,9 @@
       <c r="AU465" s="1"/>
       <c r="AV465" s="1"/>
       <c r="AW465" s="1"/>
-    </row>
-    <row r="466" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX465" s="1"/>
+    </row>
+    <row r="466" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -26640,8 +27142,9 @@
       <c r="AU466" s="1"/>
       <c r="AV466" s="1"/>
       <c r="AW466" s="1"/>
-    </row>
-    <row r="467" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX466" s="1"/>
+    </row>
+    <row r="467" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -26691,8 +27194,9 @@
       <c r="AU467" s="1"/>
       <c r="AV467" s="1"/>
       <c r="AW467" s="1"/>
-    </row>
-    <row r="468" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX467" s="1"/>
+    </row>
+    <row r="468" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -26742,8 +27246,9 @@
       <c r="AU468" s="1"/>
       <c r="AV468" s="1"/>
       <c r="AW468" s="1"/>
-    </row>
-    <row r="469" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX468" s="1"/>
+    </row>
+    <row r="469" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -26793,8 +27298,9 @@
       <c r="AU469" s="1"/>
       <c r="AV469" s="1"/>
       <c r="AW469" s="1"/>
-    </row>
-    <row r="470" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX469" s="1"/>
+    </row>
+    <row r="470" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -26844,8 +27350,9 @@
       <c r="AU470" s="1"/>
       <c r="AV470" s="1"/>
       <c r="AW470" s="1"/>
-    </row>
-    <row r="471" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX470" s="1"/>
+    </row>
+    <row r="471" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -26895,8 +27402,9 @@
       <c r="AU471" s="1"/>
       <c r="AV471" s="1"/>
       <c r="AW471" s="1"/>
-    </row>
-    <row r="472" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX471" s="1"/>
+    </row>
+    <row r="472" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -26946,8 +27454,9 @@
       <c r="AU472" s="1"/>
       <c r="AV472" s="1"/>
       <c r="AW472" s="1"/>
-    </row>
-    <row r="473" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX472" s="1"/>
+    </row>
+    <row r="473" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -26997,8 +27506,9 @@
       <c r="AU473" s="1"/>
       <c r="AV473" s="1"/>
       <c r="AW473" s="1"/>
-    </row>
-    <row r="474" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX473" s="1"/>
+    </row>
+    <row r="474" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -27048,8 +27558,9 @@
       <c r="AU474" s="1"/>
       <c r="AV474" s="1"/>
       <c r="AW474" s="1"/>
-    </row>
-    <row r="475" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX474" s="1"/>
+    </row>
+    <row r="475" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -27099,8 +27610,9 @@
       <c r="AU475" s="1"/>
       <c r="AV475" s="1"/>
       <c r="AW475" s="1"/>
-    </row>
-    <row r="476" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX475" s="1"/>
+    </row>
+    <row r="476" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -27150,8 +27662,9 @@
       <c r="AU476" s="1"/>
       <c r="AV476" s="1"/>
       <c r="AW476" s="1"/>
-    </row>
-    <row r="477" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX476" s="1"/>
+    </row>
+    <row r="477" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -27201,8 +27714,9 @@
       <c r="AU477" s="1"/>
       <c r="AV477" s="1"/>
       <c r="AW477" s="1"/>
-    </row>
-    <row r="478" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX477" s="1"/>
+    </row>
+    <row r="478" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -27252,8 +27766,9 @@
       <c r="AU478" s="1"/>
       <c r="AV478" s="1"/>
       <c r="AW478" s="1"/>
-    </row>
-    <row r="479" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX478" s="1"/>
+    </row>
+    <row r="479" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -27303,8 +27818,9 @@
       <c r="AU479" s="1"/>
       <c r="AV479" s="1"/>
       <c r="AW479" s="1"/>
-    </row>
-    <row r="480" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX479" s="1"/>
+    </row>
+    <row r="480" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -27354,8 +27870,9 @@
       <c r="AU480" s="1"/>
       <c r="AV480" s="1"/>
       <c r="AW480" s="1"/>
-    </row>
-    <row r="481" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX480" s="1"/>
+    </row>
+    <row r="481" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -27405,8 +27922,9 @@
       <c r="AU481" s="1"/>
       <c r="AV481" s="1"/>
       <c r="AW481" s="1"/>
-    </row>
-    <row r="482" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX481" s="1"/>
+    </row>
+    <row r="482" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -27456,8 +27974,9 @@
       <c r="AU482" s="1"/>
       <c r="AV482" s="1"/>
       <c r="AW482" s="1"/>
-    </row>
-    <row r="483" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX482" s="1"/>
+    </row>
+    <row r="483" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -27507,8 +28026,9 @@
       <c r="AU483" s="1"/>
       <c r="AV483" s="1"/>
       <c r="AW483" s="1"/>
-    </row>
-    <row r="484" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX483" s="1"/>
+    </row>
+    <row r="484" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -27558,8 +28078,9 @@
       <c r="AU484" s="1"/>
       <c r="AV484" s="1"/>
       <c r="AW484" s="1"/>
-    </row>
-    <row r="485" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX484" s="1"/>
+    </row>
+    <row r="485" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -27609,8 +28130,9 @@
       <c r="AU485" s="1"/>
       <c r="AV485" s="1"/>
       <c r="AW485" s="1"/>
-    </row>
-    <row r="486" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX485" s="1"/>
+    </row>
+    <row r="486" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -27660,8 +28182,9 @@
       <c r="AU486" s="1"/>
       <c r="AV486" s="1"/>
       <c r="AW486" s="1"/>
-    </row>
-    <row r="487" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX486" s="1"/>
+    </row>
+    <row r="487" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -27711,8 +28234,9 @@
       <c r="AU487" s="1"/>
       <c r="AV487" s="1"/>
       <c r="AW487" s="1"/>
-    </row>
-    <row r="488" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX487" s="1"/>
+    </row>
+    <row r="488" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -27762,8 +28286,9 @@
       <c r="AU488" s="1"/>
       <c r="AV488" s="1"/>
       <c r="AW488" s="1"/>
-    </row>
-    <row r="489" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX488" s="1"/>
+    </row>
+    <row r="489" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -27813,8 +28338,9 @@
       <c r="AU489" s="1"/>
       <c r="AV489" s="1"/>
       <c r="AW489" s="1"/>
-    </row>
-    <row r="490" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX489" s="1"/>
+    </row>
+    <row r="490" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -27864,8 +28390,9 @@
       <c r="AU490" s="1"/>
       <c r="AV490" s="1"/>
       <c r="AW490" s="1"/>
-    </row>
-    <row r="491" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX490" s="1"/>
+    </row>
+    <row r="491" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -27915,8 +28442,9 @@
       <c r="AU491" s="1"/>
       <c r="AV491" s="1"/>
       <c r="AW491" s="1"/>
-    </row>
-    <row r="492" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX491" s="1"/>
+    </row>
+    <row r="492" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -27966,8 +28494,9 @@
       <c r="AU492" s="1"/>
       <c r="AV492" s="1"/>
       <c r="AW492" s="1"/>
-    </row>
-    <row r="493" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX492" s="1"/>
+    </row>
+    <row r="493" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -28017,8 +28546,9 @@
       <c r="AU493" s="1"/>
       <c r="AV493" s="1"/>
       <c r="AW493" s="1"/>
-    </row>
-    <row r="494" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX493" s="1"/>
+    </row>
+    <row r="494" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -28068,8 +28598,9 @@
       <c r="AU494" s="1"/>
       <c r="AV494" s="1"/>
       <c r="AW494" s="1"/>
-    </row>
-    <row r="495" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX494" s="1"/>
+    </row>
+    <row r="495" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -28119,8 +28650,9 @@
       <c r="AU495" s="1"/>
       <c r="AV495" s="1"/>
       <c r="AW495" s="1"/>
-    </row>
-    <row r="496" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX495" s="1"/>
+    </row>
+    <row r="496" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -28170,8 +28702,9 @@
       <c r="AU496" s="1"/>
       <c r="AV496" s="1"/>
       <c r="AW496" s="1"/>
-    </row>
-    <row r="497" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX496" s="1"/>
+    </row>
+    <row r="497" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -28221,8 +28754,9 @@
       <c r="AU497" s="1"/>
       <c r="AV497" s="1"/>
       <c r="AW497" s="1"/>
-    </row>
-    <row r="498" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX497" s="1"/>
+    </row>
+    <row r="498" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -28272,8 +28806,9 @@
       <c r="AU498" s="1"/>
       <c r="AV498" s="1"/>
       <c r="AW498" s="1"/>
-    </row>
-    <row r="499" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX498" s="1"/>
+    </row>
+    <row r="499" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -28323,8 +28858,9 @@
       <c r="AU499" s="1"/>
       <c r="AV499" s="1"/>
       <c r="AW499" s="1"/>
-    </row>
-    <row r="500" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX499" s="1"/>
+    </row>
+    <row r="500" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="C500" s="1"/>
@@ -28374,9 +28910,10 @@
       <c r="AU500" s="1"/>
       <c r="AV500" s="1"/>
       <c r="AW500" s="1"/>
+      <c r="AX500" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AD44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:AE44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>